--- a/hasil_uji_with_tokens.xlsx
+++ b/hasil_uji_with_tokens.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Pertanyaan</t>
   </si>
@@ -41,6 +41,18 @@
   </si>
   <si>
     <t>Hybrid Token Count</t>
+  </si>
+  <si>
+    <t>Naive Prompt</t>
+  </si>
+  <si>
+    <t>Local Prompt</t>
+  </si>
+  <si>
+    <t>Global Prompt</t>
+  </si>
+  <si>
+    <t>Hybrid Prompt</t>
   </si>
   <si>
     <t>Apa tujuan Itenas sebagai institusi pendidikan tinggi?</t>
@@ -56,19 +68,107 @@
 Organisasi Kemahasiswaan Itenas diselenggarakan berdasarkan prinsip dari, oleh, dan untuk mahasiswa, dengan derajat kebebasan dan mekanisme tanggung jawab yang ditetapkan bersama antara mahasiswa dan Pimpinan Itenas. Pimpinan Itenas tetap merupakan penanggung jawab semua kegiatan di Itenas atau yang mengatasnamakan Itenas.</t>
   </si>
   <si>
-    <t>Itenas adalah Institut Teknologi Nasional yang berada di bawah naungan Yayasan Pendidikan Dayang Sumbi dan berlokasi di Bandung. Itenas memiliki visi untuk menjadi perguruan tinggi terkemuka di bidang teknologi, sains, dan seni, yang berperan aktif dalam pembangunan berkelanjutan di lingkup nasional dan global, berlandaskan nilai-nilai integritas, kualitas, dan inovasi yang tinggi.
-Misi Itenas meliputi membangun karakter bangsa melalui penyelenggaraan kegiatan tridarma perguruan tinggi yang berkualitas, menghasilkan lulusan yang unggul dalam kecerdasan intelektual serta memiliki integritas dan moral yang tinggi, menghasilkan karya ilmiah dan karya inovatif yang bermanfaat bagi kesejahteraan masyarakat, dan mengembangkan infrastruktur dan sistem manajemen yang berbasis sains dan teknologi untuk menumbuhkan suasana akademik yang kondusif.
-Tujuan Itenas adalah mengembangkan potensi sivitas akademika agar menjadi manusia yang beriman dan bertakwa kepada Tuhan Yang Maha Esa, berakhlak mulia, sehat, berilmu, cakap, kreatif, mandiri, dan menjadi warga negara yang demokratis serta bertanggung jawab, membentuk manusia yang berkualitas secara intelektual, spiritual, dan emosional, menguasai ilmu pengetahuan, teknologi, dan seni, berlandaskan pada semangat kebangsaan, sistem nilai, moral, dan watak serta peradaban yang mendukung peningkatan daya saing bangsa, menyiapkan mahasiswa menjadi warga negara beriman dan berakhlak, memiliki kemampuan akademik dan intelektual dalam bidang ilmu pengetahuan, teknologi, dan seni, yang memiliki jiwa kewirausahaan dan mampu mengembangkan potensi dirinya menjadi insan produktif bagi kehidupan pribadi, masyarakat, bangsa, dan umat manusia, mengembangkan, menyebarluaskan, dan menerapkan ilmu pengetahuan, teknologi, dan seni untuk meningkatkan kesejahteraan masyarakat dan daya saing bangsa, serta memperkaya budaya, dan mendorong terjadinya perubahan dan pembaharuan masyarakat yang lebih baik sesuai dengan perkembangan ilmu pengetahuan, teknologi, dan seni.</t>
+    <t>Itenas adalah sebuah institusi pendidikan tinggi yang dikenal sebagai Institut Teknologi Nasional dan berada di bawah naungan Yayasan Pendidikan Dayang Sumbi. Itenas memiliki tujuan untuk mengembangkan potensi sivitas akademika agar menjadi manusia yang beriman, bertakwa, berakhlak mulia, sehat, berilmu, cakap, kreatif, mandiri, dan bertanggung jawab. Selain itu, Itenas juga bertujuan untuk membentuk manusia yang berkualitas secara intelektual, spiritual, dan emosional, serta menguasai ilmu pengetahuan, teknologi, dan seni.
+Itenas juga memiliki tujuan untuk menyiapkan mahasiswa menjadi warga negara yang beriman dan berakhlak, memiliki kemampuan akademik dan intelektual dalam bidang ilmu pengetahuan, teknologi, dan seni, serta memiliki jiwa kewirausahaan. Itenas juga bertujuan untuk mengembangkan, menyebarluaskan, dan menerapkan ilmu pengetahuan, teknologi, dan seni untuk meningkatkan kesejahteraan masyarakat dan daya saing bangsa, serta memperkaya budaya. Terakhir, Itenas bertujuan untuk mendorong terjadinya perubahan dan pembaharuan masyarakat yang lebih baik sesuai dengan perkembangan ilmu pengetahuan, teknologi, dan seni.
+Visi Itenas adalah menjadi perguruan tinggi terkemuka di bidang teknologi, sains, dan seni, yang berperan aktif dalam pembangunan berkelanjutan di lingkup nasional dan global, berlandaskan nilai-nilai integritas, kualitas, dan inovasi yang tinggi. Misi Itenas meliputi membangun karakter bangsa melalui tridarma perguruan tinggi yang berkualitas, menghasilkan lulusan yang unggul dalam kecerdasan intelektual serta memiliki integritas dan moral yang tinggi, menghasilkan karya ilmiah dan inovatif yang bermanfaat bagi kesejahteraan masyarakat, dan mengembangkan infrastruktur dan sistem manajemen yang berbasis sains dan teknologi untuk menumbuhkan suasana akademik yang kondusif.</t>
   </si>
   <si>
     <t>Itenas bertujuan untuk menjadi perguruan tinggi terkemuka di bidang teknologi, sains, dan seni, yang berperan aktif dalam pembangunan berkelanjutan di lingkup nasional dan global, berlandaskan nilai-nilai integritas, kualitas, dan inovasi yang tinggi.
-Misi Itenas meliputi membangun karakter bangsa melalui kegiatan tridarma perguruan tinggi yang berkualitas, menghasilkan lulusan yang unggul dalam kecerdasan intelektual serta memiliki integritas dan moral yang tinggi, menghasilkan karya ilmiah dan inovatif yang bermanfaat bagi kesejahteraan masyarakat, serta mengembangkan infrastruktur dan sistem manajemen berbasis sains dan teknologi untuk menumbuhkan suasana akademik yang kondusif.
-Itenas juga bertujuan untuk mengembangkan potensi sivitas akademika agar menjadi manusia yang beriman dan bertakwa kepada Tuhan Yang Maha Esa, berakhlak mulia, sehat, berilmu, cakap, kreatif, mandiri, dan menjadi warga negara yang demokratis serta bertanggung jawab. Selain itu, Itenas ingin membentuk manusia yang berkualitas secara intelektual, spiritual, dan emosional, menguasai ilmu pengetahuan, teknologi, dan seni, berlandaskan pada semangat kebangsaan, sistem nilai, moral, dan watak serta peradaban yang mendukung peningkatan daya saing bangsa. Itenas juga berupaya menyiapkan mahasiswa menjadi warga negara beriman dan berakhlak, memiliki kemampuan akademik dan intelektual dalam bidang ilmu pengetahuan, teknologi, dan seni, yang memiliki jiwa kewirausahaan dan mampu mengembangkan potensi dirinya menjadi insan produktif bagi kehidupan pribadi, masyarakat, bangsa, dan umat manusia. Terakhir, Itenas bertujuan untuk mengembangkan, menyebarluaskan, dan menerapkan ilmu pengetahuan, teknologi, dan seni untuk meningkatkan kesejahteraan masyarakat dan daya saing bangsa, serta memperkaya budaya, dan mendorong terjadinya perubahan dan pembaharuan masyarakat yang lebih baik sesuai dengan perkembangan ilmu pengetahuan, teknologi, dan seni.</t>
+Misi Itenas meliputi membangun karakter bangsa melalui kegiatan tridarma perguruan tinggi yang berkualitas, menghasilkan lulusan unggul dalam kecerdasan intelektual serta berintegritas dan bermoral tinggi, menghasilkan karya ilmiah dan inovatif yang bermanfaat bagi kesejahteraan masyarakat, serta mengembangkan infrastruktur dan sistem manajemen berbasis sains dan teknologi untuk menumbuhkan suasana akademik yang kondusif.
+Itenas juga bertujuan mengembangkan potensi sivitas akademika agar menjadi manusia yang beriman, bertakwa, berakhlak mulia, sehat, berilmu, cakap, kreatif, mandiri, dan menjadi warga negara yang demokratis serta bertanggung jawab. Selain itu, Itenas ingin membentuk manusia yang berkualitas secara intelektual, spiritual, dan emosional, menguasai ilmu pengetahuan, teknologi, dan seni, berlandaskan pada semangat kebangsaan, sistem nilai, moral, dan watak serta peradaban yang mendukung peningkatan daya saing bangsa. Itenas juga berupaya menyiapkan mahasiswa menjadi warga negara beriman dan berakhlak, memiliki kemampuan akademik dan intelektual dalam bidang ilmu pengetahuan, teknologi, dan seni, yang memiliki jiwa kewirausahaan dan mampu mengembangkan potensi dirinya menjadi insan produktif bagi kehidupan pribadi, masyarakat, bangsa, dan umat manusia. Itenas juga bertujuan mengembangkan, menyebarluaskan, dan menerapkan ilmu pengetahuan, teknologi, dan seni untuk meningkatkan kesejahteraan masyarakat dan daya saing bangsa, serta memperkaya budaya, dan mendorong terjadinya perubahan dan pembaharuan masyarakat yang lebih baik sesuai dengan perkembangan ilmu pengetahuan, teknologi, dan seni.</t>
   </si>
   <si>
     <t xml:space="preserve">Itenas bertujuan untuk mengembangkan potensi sivitas akademika agar menjadi manusia yang beriman, bertakwa, berakhlak mulia, sehat, berilmu, cakap, kreatif, mandiri, dan bertanggung jawab. Selain itu, Itenas juga bertujuan untuk membentuk manusia yang berkualitas secara intelektual, spiritual, dan emosional, menguasai ilmu pengetahuan, teknologi, dan seni, berlandaskan pada semangat kebangsaan, sistem nilai, moral, dan watak serta peradaban yang mendukung peningkatan daya saing bangsa.
 Itenas juga bertujuan untuk menyiapkan mahasiswa menjadi warga negara beriman dan berakhlak, memiliki kemampuan akademik dan intelektual dalam bidang ilmu pengetahuan, teknologi, dan seni, yang memiliki jiwa kewirausahaan dan mampu mengembangkan potensi dirinya menjadi insan produktif bagi kehidupan pribadi, masyarakat, bangsa, dan umat manusia. Tujuan lainnya adalah mengembangkan, menyebarluaskan, dan menerapkan ilmu pengetahuan, teknologi, dan seni untuk meningkatkan kesejahteraan masyarakat dan daya saing bangsa, serta memperkaya budaya, serta mendorong terjadinya perubahan dan pembaharuan masyarakat yang lebih baik sesuai dengan perkembangan ilmu pengetahuan, teknologi, dan seni.
 </t>
+  </si>
+  <si>
+    <t>---Role---
+You are a helpful assistant responding to user query about Document Chunks provided provided in JSON format below.
+---Goal---
+Generate a concise response based on Document Chunks and follow Response Rules, considering both the conversation history and the current query. Summarize all information in the provided Document Chunks, and incorporating general knowledge relevant to the Document Chunks. Do not include information not provided by Document Chunks.
+When handling content with timestamps:
+1. Each piece of content has a "created_at" timestamp indicating when we acquired this knowledge
+2. When encountering conflicting information, consider both the content and the timestamp
+3. Don't automatically prefer the most recent content - use judgment based on the context
+4. For time-specific queries, prioritize temporal information in the content before considering creation timestamps
+---Conversation History---
+---Document Chunks(DC)---
+[{"id": 1, "content": "sebagai\nsarana dan wadah untuk:\na. menampung dan menyalurkan aspirasi mahasiswa,\nmenetapkan garis-garis besar program dan kegiatan\nkemahasiswaan;\nb. melaksanakan kegiatan kemahasiswaan;\nc. melaksanakan kegiatan yang terkait dengan penerapan\nkeilmuan dan keahlian, pengabdian kepada masyarakat, dan/\natau sesuai dengan bakat dan peminatan mahasiswa;\nd. memfasilitasi komunikasi antar mahasiswa;\ne. mengembangkan potensi jati diri mahasiswa sebagai insan\nakademis, calon ilmuwan, dan intelektual yang berguna di\nmasa depan;\nf. mengembangkan pelatihan keterampilan berorganisasi,\nmanajemen, dan kepemimpinan mahasiswa;\ng. memelihara dan mengembangkan ilmu, teknologi, dan seni\nyang dilandasi oleh norma-norma agama, akademis, etika,\nmoral, dan wawasan kebangsaan.\n2. Organisasi Kemahasiswaan Itenas diselenggarakan terutama\nberdasarkan prinsip dari, oleh, dan untuk mahasiswa.\n3. Derajat kebebasan dan mekanisme tanggung jawab Organisasi\nKemahasiswaan Itenas terhadap Itenas ditetapkan bersama\nantara mahasiswa dan Pimpinan Itenas, dengan tetap berpedoman\nbahwa Pimpinan Itenas merupakan penanggung jawab semua\nkegiatan di Itenas dan/atau yang mengatasnamakan Itenas.\nPrinsip Penyelenggaraan Organisasi\nPasal 15\n1. Organisasi Kemahasiswaan Itenas menganut asas terbuka, tidak\ndiskriminatif, mandiri, adil, kekeluargaan, efektif, efisien, dan\ntransparan.\n2. Kebijakan dan kegiatan Organisasi Kemahasiswaan Itenas\nditentukan oleh anggota dalam organisasi yang bersangkutan\n\n--- Halaman 177 ---\n176\n1202\nsanetI\nawsisahaM\nmumU\nnaudnaP\ndengan mengacu kepada peraturan Itenas.\n3. Kebijakan dan kegiatan Organisasi Kemahasiswaan Itenas tidak\nbertentangan dengan peraturan Itenas, peraturan yang berlaku di\nNegara Republik Indonesia dan etika masyarakat.\n4. Pengurus Organisasi Kemahasiswaan Itenas adalah mahasiswa\nyang memiliki prestasi akademik yang baik, tidak sedang\nmenjalani sanksi akademik dan dapat mengelola waktu dengan\nbaik.\nKeabsahan Organisasi Kemahasiswaan Itenas\nPasal 16\n1. Organisasi Kemahasiswaan Itenas harus terdaftar secara resmi\ndi Biro Kemahasiswaan dan diijinkan secara sah melalui Surat\nKeputusan Rektor.\n2. Anggaran Dasar dan Rumah Tangga Organisasi Kemahasiswaan\nItenas disahkan oleh Rektor.\n3. Pendaftaran Organisasi Kemahasiswaan Itenas mengikuti\nketentuan yang diatur oleh Wakil Rektor Bidang Akademik dan\nKemahasiswaan.\nHak &amp; Kewajiban Organisasi Kemahasiswaan Itenas\nPasal 17\n1. Organisasi Kemahasiswaan Itenas berhak memperoleh pelayanan,\npembinaan, dan izin menggunakan fasilitas Itenas, sesuai dengan\nperaturan penggunaan fasillitas Itenas.\n2. Organisasi Kemahasiswaan Itenas mempunyai kewajiban:\na. mematuhi ketentuan dan peraturan yang berlaku di Itenas,\nNegara Republik Indonesia, dan etika masyarakat;\nb. melaksanakan kegiatan secara bersungguh-sungguh dan\nbertanggung jawab serta bermanfaat bagi mahasiswa, baik\nperorangan maupun kelompok/organisasi serta bermanfaat\nbagi kegiatan pendidikan Itenas;\nc. mendukung suasana dan proses pembelajaran yang\nmenunjang keberhasilan proses pendidikan;\n\n--- Halaman 178 ---\n177\nItenas\nUndergraduate\nGuide\n2021\nd. menjaga dan menegakkan nama baik serta wibawa Itenas;\ne. membuat program kerja dan anggaran tahunan secara tertulis\nsesuai peraturan yang berlaku disampaikan kepada BKA;\nf. membuat laporan hasil kerja tahunan secara tertulis sesuai\nperaturan yang berlaku disampaikan;\ng. memberikan laporan secara tertulis sesuai peraturan\nyang berlaku, selambat-lambatnya 1 (satu) minggu setelah\npenyelenggaraan setiap kegiatan disampaikan ke BKA\nHimpunan Mahasiswa Program Studi\nPasal 18\n1. Himpunan Mahasiswa Prodi adalah kelengkapan organisasi\nkemahasiswaan di tingkat Prodi yang kegiatannya berdasarkan\npada keilmuan dan keprofesian.\n2. Seluruh mahasiswa yang terdaftar secara sah pada suatu Prodi\nadalah merupakan anggota himpunan Prodi tersebut.\n3. Pengurus inti Himpunan Mahasiswa Prodi terdiri atas Ketua,\nSekretaris dan Bendahara.\n4. Pengurus inti Himpunan Mahasiswa Prodi harus memenuhi\nsyarat sebagai berikut:\na. mahasiswa aktif yang memiliki prestasi akademik dengan IPK\nsekurang-kurangnya 2,75 (dua koma tujuh lima);\nb. telah menjadi mahasiswa sekurang-kurangnya 4 (empat)\nsemester; dan\nc. mempunyai integritas, kepribadian dan berbudi luhur.\n5. Pengurus Himpunan Mahasiswa Prodi disahkan berdasarkan\nSurat Keputusan Dekan berdasarkan usulan dari himpunan.\n6. Pengurus Himpunan Mahasiswa Prodi dilantik oleh Dekan\nFakultas.\n7. Ketua Himpunan Mahasiswa Prodi bertanggung jawab kepada\nDekan.\n8. Masa bakti pengurus Himpunan Mahasiswa Prodi 1 (satu) tahun\ndan khusus untuk Ketua Himpunan", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 2, "content": "pendidikan, standar nasional\n\n--- Halaman 10 ---\n9\nItenas\nUndergraduate\nGuide\n2021\npenelitian, dan standar nasional Semester antara adalah semester\npengabdian kepada masyarakat. yang setara dengan semester\ngasal/genap, yang dapat\nStandar Pendidikan Tinggi Itenas diselenggarakan diantara semester\nadalah sejumlah standar di Itenas genap dan semester gasal tahun\nyang melebihi Standar Nasional akademik berikutnya.\nPendidikan Tinggi.\nPenelitian adalah kegiatan yang\nMahasiswa adalah peserta didik dilakukan menurut kaidah dan\npada program pendidikan tinggi metode ilmiah secara sistematis\nyang terdaftar di Itenas dan untuk memperoleh informasi,\ndicatatkan pada Pangkalan Data data, dan keterangan yang\nPendidikan Tinggi (PD Dikti). berkaitan dengan pemahaman\ndan/atau pengujian suatu cabang\nPembelajaran adalah proses pengetahuan dan teknologi.\ninteraksi mahasiswa dengan dosen\ndan sumber belajar pada suatu Penelitian unggulan Itenas\nlingkungan belajar. adalah penelitian dalam bidangbidang unggulan yang ditetapkan\nKurikulum adalah seperangkat oleh Itenas, yang sesuai\nrencana dan pengaturan mengenai dengan kebijakan dan program\ncapaian pembelajaran lulusan, pembangunan lokal/nasional/\nbahan kajian, proses, dan penilaian internasional melalui pemanfaatan\nyang digunakan sebagai pedoman kepakaran dan sarana/prasarana\npenyelenggaraan program studi. penelitian Itenas, dan/atau sumber\ndaya setempat.\nSemester adalah satuan waktu\nkegiatan yang terdiri atas 14 Pengabdian kepada masyarakat\n(empat belas) sampai 16 (enam adalah kegiatan sivitas akademika\nbelas) minggu kuliah dan/atau yang memanfaatkan ilmu\nkegiatan terjadwal lainnya, berikut pengetahuan dan teknologi\nkegiatan iringannya, termasuk untuk memajukan kesejahteraan\n2 (dua) sampai 3 (tiga) minggu masyarakat dan mencerdaskan\nkegiatan penilaian. kehidupan bangsa.\n\n--- Halaman 11 ---\n10\n1202\nsanetI\nawsisahaM\nmumU\nnaudnaP\nPengabdian kepada masyarakat atau program pendidikan profesi\nunggulan Itenas adalah dalam satu rumpun disiplin ilmu\npengabdian kepada masyarakat pengetahuan, teknologi, dan/atau\ndalam bidang-bidang unggulan seni.\nyang ditetapkan oleh Itenas, yang\nsesuai dengan kebijakan dan Satuan adalah organ dalam\nprogram pembangunan lokal/ struktur organisasi Itenas yang\nnasional/internasional melalui melaksanakan suatu program\npemanfaatan kepakaran dan kegiatan.\nsarana/prasarana Itenas, dan/atau\nsumber daya setempat. Unit Pelaksana Teknis adalah\nunsur penunjang teknis kegiatan\nSivitas akademika adalah pendidikan di Itenas.\nkelompok atau warga masyarakat\nakademik yang terdiri atas dosen Biro adalah unsur penunjang\ndan mahasiswa. dalam pelaksanaan administrasi\nItenas.\nGelar adalah sebutan yang\ndiberikan kepada lulusan program Program Studi adalah kesatuan\npendidikan tinggi yang sesuai kegiatan pendidikan dan\ndengan ketentuan perundang- pembelajaran yang memiliki\nundangan. kurikulum dan metode\npembelajaran tertentu dalam\nOrgan Itenas, selanjutnya satu jenis program pendidikan\ndisebut organ, adalah unit akademik dan/atau program\ndalam organisasi Itenas yang pendidikan profesi.\nmenjalankan fungsi Itenas, baik\nsendiri maupun bersama-sama. Laboratorium/Studio adalah\nsarana dan prasarana fisik\nPejabat struktural adalah pegawai yang digunakan untuk kegiatan\ntetap Itenas yang diangkat dan praktikum/studio serta\ndiberhentikan oleh Yayasan pengembangan keilmuan pada\nuntuk memimpin suatu organ satu atau lebih bidang kajian.\nItenas dalam periode waktu\ntertentu, dengan tugas, tanggung Dosen adalah pegawai yang\njawab, wewenang, dan hak yang berfungsi sebagai pendidik\nditetapkan oleh Yayasan. profesional dan ilmuwan dengan\ntugas utama mentransformasikan,\nFakultas adalah himpunan mengembangkan, dan\nsumber daya pendukung, yang menyebarluaskan ilmu\nmenyelenggarakan dan mengelola pengetahuan, teknologi, dan seni\nprogram pendidikan akademik dan/ melalui pendidikan, penelitian, dan\n\n--- Halaman 12 ---\n11\nItenas\nUndergraduate\nGuide\n2021\npengabdian kepada masyarakat.\nTenaga kependidikan adalah\npegawai yang diangkat untuk\nmenunjang penyelenggaraan\npendidikan tinggi bidang akademik\nyaitu pustakawan, tenaga\nadministrasi, laboran, teknisi, dan\npranata teknologi informasi.\nTenaga nonkependidikan adalah\npegawai yang diangkat untuk\nmenunjang penyelenggaraan\npendidikan tinggi bidang\nnonakademik yaitu tenaga bidang\npenggunaan dan pemeliharaan\nkendaraan, tenaga bidang\nkebersihan, dan tenaga bidang\nkeamanan.\nKomisi disiplin adalah tim adhoc\nyang dibentuk untuk memberikan\npertimbangan dan/atau usul bagi\npenjatuhan sanksi kepada pegawai\ndan/atau mahasiswa yang\nmelakukan pelanggaran peraturan.\nAlumni adalah mahasiswa yang\ndinyatakan telah menyelesaikan\npendidikannya pada program\npendidikan yang diselenggarakan\noleh Atenas dan Itenas.\nSenat Akademik adalah badan\nnormatif yang menjalankan fungsi\npenyusunan, pertimbangan, dan\npengawasan kebijakan akademik.\n\n--- Halaman 13 ---\n12\n1202", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 3, "content": "teraan mahasiswa, dan\nbakti sosial bagi masyarakat;\nh. Norma adalah suatu ukuran atau patokan yang harus dipatuhi\noleh seseorang dalam bertindak dan bertingkah laku dalam\nmasyarakat;\ni. Minuman keras adalah segala jenis minuman yang mengandung\nalkohol dan zat-zat lainnya yang membahayakan kesehatan\nmenurut peraturan perundang-undangan yang berlaku;\nj. Narkotika adalah zat atau obat yang berasal dari tanaman atau\nbukan tanaman baik sintetis maupun semi sintetis yang dapat\nmenyebabkan penurunan atau perubahan kesadaran, hilangnya\nrasa, mengurangi sampai menghilangkan rasa nyeri, dan dapat\n\n--- Halaman 168 ---\n167\nItenas\nUndergraduate\nGuide\n2021\nmenimbulkan ketergantungan, sebagaimana diatur dalam\nUndang-Undang Republik Indonesia Nomor 35 Tahun 2009\ntentang Narkotika;\nk. Psikotropika adalah zat atau obat, baik alamiah maupun sintetis\nbukan narkotika, yang berkhasiat psikoaktif melalui pengaruh\nselektif pada susunan saraf pusat yang menyebabkan perilaku\nkhas pada akivitas mental dan perilaku, sebagaiman yang diatur\ndalam Undang-Undang Republik Indonesia Nomor 5 tahun 1997\ntentang Psikotropika atau perundang-undangan dan peraturan\nlainnya yang diterbitkan oleh Pemerintah Republik Indonesia;\nl. Judi adalah permainan yang menggunakan alat bantu baik secara\nlangsung maupun tidak langsung sebagai media taruhan dengan\nuang atau barang lainnya yang mempunyai nilai atau harga dan\nmengakibatkan kerugian atau keuntungan salah satu pihak;\nm. Senjata adalah segala jenis alat untuk membela diri, menakutnakuti atau untuk melakukan penyerangan terhadap orang lain,\nyang jika digunakan dengan sengaja atau karena kelalaian dapat\nmengakibatkan luka ringan, luka parah, dampak psikologis, atau\nbahkan dapat mengakibatkan meninggalnya seseorang;\nn. Bahan peledak adalah segala macam bahan atau zat yang\nberbentuk padat, cair, dan atau gas yang dapat menimbulkan\nledakan dan membahayakan bagi manusia, gedung, atau\nlingkungan dan yang dilarang oleh undang-undang;\no. Tindakan kekerasan adalah mengancam/menakut-nakuti/\nmemaksa/melawan/intimidasi, berkelahi, memukul dengan\ntangan atau benda keras, menampar/menggampar, meninju,\nmenendang, melempar dengan benda keras atau barang\nberbahaya lainnya, menikam dan tindakan kekerasan lainnya\ndengan tujuan untuk membahayakan orang lain;\np. Pelanggaran kesusilaan adalah pelanggaran terhadap normanorma kesusilaan dan pelanggaran terhadap peraturan\nperundang-undangan yang mengatur tentang kesusilaan.\nq. Warga Itenas adalah seluruh unsur yang terdiri dari pimpinan,\ndosen, tenaga kependidikan dan non kependidikan dan\nmahasiswa.\n\n--- Halaman 169 ---\n168\n1202\nsanetI\nawsisahaM\nmumU\nnaudnaP\n\n\nBAB II\nHAK DAN KEWAJIBAN MAHASISWA\nHak Mahasiswa\nPasal 2\nSelama masa pendidikannya mahasiswa mempunyai hak:\na. menggunakan kebebasan akademik secara bertanggung\njawab untuk menuntut ilmu dan mengkaji ilmu sesuai dengan\nnorma dan etika yang berlaku di Itenas;\nb. memperoleh pengalaman belajar dan layanan bidang\nakademik sesuai dengan minat, bakat, dan kemampuan;\nc. memanfaatkan fasilitas dan layanan Itenas dalam mendukung\nkelancaran proses belajar sesuai dengan ketentuan yang\nberlaku;\nd. mendapat bimbingan dari dosen dalam rangka penyelesaian\nstudinya selama masa studinya;\ne. mendapat beasiswa bagi mereka yang berprestasi dan atau\nberasal dari keluarga yang kurang mampu jika memenuhi\npersyaratan yang berlaku di Itenas;\nf. memperoleh layanan informasi yang berkaitan dengan\nprogram studi yang diikuti;\ng. mengikuti kegiatan organisasi mahasiswa yang ada di Itenas;\nh. melaksanakan merdeka belajar untuk pemenuhan beban\nbelajar di program studi asal, lintas program studi di lingkungan\nItenas, dan/atau di luar Itenas sesuai dengan peraturan yang\nberlaku di Itenas;\ni. pindah ke program studi lain dalam lingkungan Itenas dengan\nmengikuti ketentuan peraturan yang berlaku di Itenas;\nj. pindah ke perguruan tinggi lain.\n\n--- Halaman 170 ---\n169\nItenas\nUndergraduate\nGuide\n2021\nKewajiban Mahasiswa\nPasal 3\nMahasiswa berkewajiban untuk:\na. menjunjung tinggi kehormatan, martabat, dan nama baik\nItenas;\nb. menjunjung tinggi hukum dan kode etik, serta nilai-nilai\nagama dan etika, dan peraturan perundang-undangan yang\nditerbitkan oleh Pemerintah dan Itenas;\nc. memegang teguh dan menghargai norma dan etika akademik;\nd. menjaga dan memelihara kebersihan, ketertiban, keindahan,\ndan keamanan sarana dan prasarana Itenas;\ne. menjaga sikap, perilaku dan etika dalam berhubungan/\nberkomunikasi dengan Dosen dan Pegawai Tenaga\nKependidikan dan Non Kependidikan;\nf. menjaga sikap dan hubungan baik antar sesama mahasiswa;\ng. memelihara dan meningkatkan keutuhan, kekompakan,\npersatuan dan kesatuan warga it", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 4, "content": "– Jl. Setiabudi – Jl. Cihampelas – Jl.\nSiliwangi – Simpang Dago – Jl. Dipati Ukur – Jl. Singa Perbangsa – Monumen\nPerjuangan – Jl. Japati – Lapangan Gasibu (Surapati) – Jl. Surapati (Suci) – Jl.\nPHH. Mustofa (Suci) – Terminal Cicaheum\nCoklat – Putih (Kijang)\nCICAHEUM – CIWASTRA\nTerminal Cicaheum – Jl. PHH. Mustofa (Suci) – Jl. Surapati (Suci) – Jl. Sentot\nAlibasyah – Jl. Diponegoro – Jl. WR. Supratman – Jl. Ahmad Yani – Jl. Jakarta\n– Jl. Kiara Condong – Jl. Terusan Kiara Condong – Jl. Margacinta – Jl. Ciwastra –\nTerminal Ciwastra\nCIWASTRA – CICAHEUM\nTerminal Ciwastra – Jl. Ciwastra – Jl. Margacinta – Jl. Terusan Kiara Condong –\nJl. Kiara Condong – Jl. Jakarta – Jl. WR. Supratman – Jl. Diponegoro – Jl. Sentot\nAlibasyah Lapangan Gasibu – Jl. Surapati (Suci) – *Jl. PHH. Mustofa (Suci) –\n*Terminal Cicaheum\nHijau – Hitam (06)\nCICAHEUM – LEDENG\nTerminal Cicaheum – Jl. PHH. Mustofa (Suci) – Jl. Katamso – Jl. WR. Supratman\n– Jl. Diponegoro – Jl. Sulanjana – Jl. Tamansari – Jl. Siliwangi – Jl. Cihampelas\n– Jl. Lamping – Jl. Cipaganti – Jl. Setiabudi – Jl. Karang Sari – Jl. Sukajadi – Jl.\nSetiabudi – Terminal Ledeng\nLEDENG – CICAHEUM\nTerminal Ledeng – Jl. Setiabudi – Jl. Cihampelas – Jl. Siliwangi – Jl. Sumur\nBandung – Jl. Tamansari – Jl. Sulanjana – Jl. Diponegoro – Jl. WR. Supratman\n– Jl. Katamso – Jl. Pahlawan – Jl. Cikutra – Jl. PHH. Mustofa (Suci) – Terminal\nCicaheum\nTRANS METRO BANDUNG (CICAHEUM - SARIJADI)\nTerminal Cicaheum – Jl. PHH. Mustofa (suci) – Jl. Surapati (Suci) – Gasibu – Fly\nOver – Pasteur – Sarijadi (PP)\n\n--- Halaman 122 ---\nB A B VIII 121\nPERATURAN\nAKADEMIK\n“I follow three rules: Do the right thing,\ndo the best you can, and always show\npeople you care.”\n- Lou Holtz\nItenas\nUndergraduate\nGuide\n2021\n\n--- Halaman 123 ---\n122\n1202\nsanetI\nawsisahaM\nmumU\nnaudnaP\nKEPUTUSAN\nREKTOR INSTITUT TEKNOLOGI NASIONAL\nNomor: 108/N.07.04/Rektorat/Itenas/VIII/2020\ntentang\nPERATURAN AKADEMIK PROGRAM SARJANA\nINSTITUT TEKNOLOGI NASIONAL\n-----------------------------------------------------------\nREKTOR INSTITUT TEKNOLOGI NASIONAL\nMenimbang :\n1. Bahwa pendidikan di Institut Teknologi Nasional harus\ndilaksanakan berpedoman pada Peraturan menteri\nPendidikan dan Kebudayaan Republik Indonesia Nomor 03\nTahun 2020 tentang Standar Nasional Pendidikan Tinggi\ndan Surat Keputusan Yayasan Pendidikan Dayang Sumbi\nNomor 182/Kpts/YPDS/V/2020 tentang Standar Pendidikan\nTinggi Institut Teknologi Nasional;\n2. Bahwa pelaksanaan pembelajaran pada program studi di\nlingkungan Itenas mengacu kepada Kurikulum Tahun 2017;\n3. Bahwa berdasarkan kedua butir di atas perlu dilakukan\nrevisi Surat Keputusan Rektor Nomor Nomor 220/N.07.04/\nRektorat/ltenas/XI/2017 tentang Peraturan Akademik\nProgram Sarjana.\n\n--- Halaman 124 ---\n123\nItenas\nUndergraduate\nGuide\n2021\nMengingat :\n1. Undang-Undang Republik Indonesia Nomor 12 Tahun 2012\ntentang Pendidikan Tinggi (Lembaran Negara Republik\nIndonesia Tahun 2012 Nomor 158, Tambahan Lembaran\nNegara Republik Indonesia Nomor 5336);\n2. Peraturan Pemerintah Republik Indonesia Nomor 4 Tahun\n2014 tentang Penyelenggaraan Pendidikan Tinggi dan\nPengelolaan Perguruan Tinggi (Lembaran Negara Republik\nIndonesia Tahun 2014 Nomor 16, Tambahan Lembaran\nNegara Republik Indonesia Nomor 5500);\n3. Peraturan Menteri Pendidikan dan Kebudayaan Republik\nIndonesia Nomor 03 Tahun 2020 tentang Standar Nasional\nPendidikan Tinggi ( Berita Negara Republik Indonesia\nTahun 2020 Nomor 47);\n4. Keputusan Peng", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 5, "content": "askan, apabila mencapai IPK 2,76 (dua koma tujuh enam)\nsampai dengan 3,00 (tiga koma nol nol);\nb. Sangat memuaskan, apabila mencapai IPK 3,01 (tiga koma nol\nsatu) sampai dengan 3,50 (tiga koma lima nol); atau\nc. Dengan pujian, apabila mencapai IPK lebih dari 3,50 (tiga koma\nlima nol), dan masa studi selama-lamanya 9 (sembilan) semester.\n2. Kewenangan menetapkan predikat kelulusan mengikuti\nketentuan sebagai berikut :\na. Predikat dengan pujian ditetapkan pada tingkat Itenas oleh\nRektor;\nb. Predikat sangat memuaskan ditetapkan pada tingkat fakultas\noleh Dekan;\nc. Predikat memuaskan ditetapkan pada tingkat program studi\noleh Ketua Program Studi.\nPasal 45\nHak lulusan program sarjana adalah memperoleh :\na. Ijazah;\nb. Gelar;\nc. Transkrip akademik;\n\n--- Halaman 149 ---\n148\n1202\nsanetI\nawsisahaM\nmumU\nnaudnaP\nd. Transkrip kegiatan kemahasiswaan;\ne. Surat Keterangan Pendamping Ijazah (SKPI); dan\nf. Sertifikat kompetensi (jika ada).\nGelar Akademik\nPasal 46\n1. Gelar akademik dan singkatannya dicantumkan pada ijazah;\n2. Penggunaan gelar akademik sesuai dengan peraturan yang\nberlaku.\nIjazah\nPasal 47\n1. Ijazah diberikan kepada mahasiswa sebagai tanda bukti telah\nmenyelesaikan pendidikan;\n2. Ijazah ditanda tangani oleh Rektor dan Dekan Fakultas.\nPasal 48\n1. Ijazah/surat tanda lulus program sarjana hanya dibuat satu kali;\n2. Ijazah/surat tanda lulus program sarjana yang hilang akan diganti\ndengan surat keterangan;\n3. Alumni yang mengaku kehilangan ijazah dapat mengajukan\npermohonan pembuatan surat keterangan sebagai pengganti\nijazah yang hilang kepada Biro Akademik, dengan menyertakan\nsurat keterangan kehilangan dari kepolisian;\n4. Biro Akademik menerbitkan surat keterangan tersebut setelah\nmeneliti bahwa alumni yang bersangkutan benar-benar lulusan\nItenas;\n5. Surat keterangan sebagai pengganti ijazah yang hilang\nditandatangani oleh Rektor dan Dekan.\n\n--- Halaman 150 ---\n149\nItenas\nUndergraduate\nGuide\n2021\nTranskrip Akademik\nPasal 49\n1. Transkrip akademik adalah transkrip untuk Sistem Kredit\nSemester;\n2. Transkrip akademik diberikan kepada lulusan;\n3. Transkrip akademik menunjukkan penilaian hasil belajar seluruh\nsemester yaitu nilai seluruh mata kuliah, jumlah sks yang\nditempuh, IPK, tanggal kelulusan, predikat kelulusan, dan judul\nTugas Akhir.\nTranskrip Kegiatan Kemahasiswaan\nPasal 50\n1. Transkrip kegiatan kemahasiswaan adalah transkrip untuk\nSistem Kredit Kemahasiswaan;\n2. Transkrip kegiatan kemahasiswaan diberikan kepada lulusan;\n3. Transkrip kegiatan kemahasiswaan menunjukkan penilaian hasil\nkegiatan kemahasiswaan selama studi di Itenas.\nSurat Keterangan Pendamping Ijazah\nPasal 51\n1. Surat Keterangan Pendamping Ijazah (SKPI) adalah surat\npernyataan resmi yang dikeluarkan oleh Itenas, berisi informasi\ntentang capaian pembelajaran lulusan, sistem pendidikan, dan\nkualifikasi dari lulusan pendidikan tinggi bergelar;\n2. SKPI juga memuat informasi tentang Sistem Kredit\nKemahasiswaan, jenis kegiatan dalam SKK, dan prestasi\nmahasiswa, serta informasi lainnya yang menjelaskan capaian\npembelajaran lulusan;\n3. SKPI ditulis dalam Bahasa Indonesia dan Bahasa Inggris.\n\n--- Halaman 151 ---\n150\n1202\nsanetI\nawsisahaM\nmumU\nnaudnaP\nSertifikat Kompetensi\nPasal 52\n1. Sertifikat kompetensi sebagaimana dimaksud Pasal 45 dapat\ndiberikan kepada lulusan program sarjana sesuai dengan keahlian\ndalam cabang ilmunya yang telah memenuhi syarat dan/atau\nmemiliki prestasi di luar program studinya;\n2. Sertifikat kompetensi sebagaimana dimaksud pada ayat 1 pasal\nini diterbitkan oleh Itenas bekerja sama dengan organisasi profesi,\nlembaga pelatihan, atau lembaga sertifikasi yang terakreditasi.\n\n\nBAB X\nPELANGGARAN TERHADAP NORMA MASYARAKAT AKADEMIK\nJenis Pelanggaran\nPasal 53\n1. Mahasiswa wajib menjunjung tinggi nilai kejujuran, etika dalam\nmasyarakat serta norma masyarakat akademik;\n2. Mahasiswa tidak boleh melakukan perbuatan yang melanggar\nnorma masyarakat akademik, antara lain :\na. Mencontek atau mencoba menggunakan bahan-bahan,\ninformasi, atau alat bantu studi lainnya tanpa ijin dari asisten atau\ndosen yang berkepentingan dalam kegiatan akademik;\nb. Memalsukan nilai atau transkrip akademik, ijazah, Kartu Tanda\nMahasiswa, Kartu Studi Mahasiswa, tugas-tugas dalam rangka\nperkuliahan, surat keterangan, laporan dan/atau tanda tangan", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}]
+---Response Rules---
+- Target format and length: Multiple Paragraphs
+- Use markdown formatting with appropriate section headings
+- Please respond in the same language as the user's question.
+- Ensure the response maintains continuity with the conversation history.
+- If you don't know the answer, just say so.
+- Do not include information not provided by the Document Chunks.
+- Addtional user prompt: n/a
+Response:
+user: Apa tujuan Itenas sebagai institusi pendidikan tinggi?</t>
+  </si>
+  <si>
+    <t>---Role---
+You are a helpful assistant responding to user query about Knowledge Graph and Document Chunks provided in JSON format below.
+---Goal---
+Generate a concise response based on Knowledge Base and follow Response Rules, considering both the conversation history and the current query. Summarize all information in the provided Knowledge Base, and incorporating general knowledge relevant to the Knowledge Base. Do not include information not provided by Knowledge Base.
+When handling relationships with timestamps:
+1. Each relationship has a "created_at" timestamp indicating when we acquired this knowledge
+2. When encountering conflicting relationships, consider both the semantic content and the timestamp
+3. Don't automatically prefer the most recently created relationships - use judgment based on the context
+4. For time-specific queries, prioritize temporal information in the content before considering creation timestamps
+---Conversation History---
+---Knowledge Graph and Document Chunks---
+-----Entities(KG)-----
+```json
+[{"id": 1, "entity": "Akademik", "type": "category", "description": "Akademik adalah kegiatan yang terkait dengan pendidikan di Itenas.", "created_at": "2025-07-22 15:09:16", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 2, "entity": "Lab. Multimedia", "type": "organization", "description": "Lab. Multimedia adalah sebuah laboratorium di Itenas.", "created_at": "2025-07-22 15:10:46", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 3, "entity": "Itenas", "type": "organization", "description": "Itenas adalah sebuah institusi pendidikan tinggi yang dikenal sebagai Institut Teknologi Nasional. Itenas berada di bawah naungan Yayasan Pendidikan Dayang Sumbi dan memiliki peraturan kemahasiswaan serta keputusan rektor yang jelas. Sebagai sebuah perguruan tinggi, Itenas memiliki berbagai fakultas dan program studi yang menawarkan pendidikan dengan standar yang melebihi standar nasional. Itenas juga memiliki berbagai organisasi kemahasiswaan, termasuk Himpunan Mahasiswa Prodi, Unit Kegiatan Mahasiswa, dan Keluarga Mahasiswa Itenas, yang berfungsi sebagai wadah untuk mengembangkan kemampuan dan kreativitas mahasiswa.\n\nItenas memiliki sistem administrasi akademik yang terstruktur, termasuk Sistem Kredit Semester dan Sistem Kredit Kemahasiswaan, yang digunakan untuk mengukur partisipasi mahasiswa dalam kegiatan kemahasiswaan. Itenas juga menyediakan berbagai layanan dan fasilitas untuk mahasiswanya, termasuk bimbingan dan konseling, pengembangan keprofesian, bantuan asuransi kecelakaan, dana kemahasiswaan, dan layanan kesehatan. Selain itu, Itenas juga memiliki berbagai unit kegiatan mahasiswa dan organisasi kemahasiswaan yang aktif, seperti Himpunan Mahasiswa Pencinta Alam dan Koperasi Mahasiswa.\n\nItenas memiliki peraturan akademik dan sistem kredit kemahasiswaan yang jelas, serta prosedur dan ketentuan untuk mahasiswanya, termasuk prosedur cuti kuliah dan ujian khusus. Itenas juga menerbitkan panduan untuk mahasiswa baru dan mahasiswa secara umum, serta pedoman untuk mahasiswanya. Itenas menyelenggarakan pendidikan dengan menerapkan Sistem Kredit Semester dan Sistem Kredit Kemahasiswaan, dan memiliki berbagai kegiatan akademik, termasuk ujian dan penelitian.\n\nDalam hal kegiatan kemahasiswaan, Itenas menjadi lokasi kegiatan organisasi mahasiswa, seperti Himpunan Mahasiswa Teknik Informatika (HMIF) dan Himpunan Mahasiswa Elektro. Itenas juga menyediakan fasilitas pendukung untuk mahasiswa, termasuk laboratorium, perpustakaan, dan prasarana olahraga. Itenas memiliki berbagai program studi dan mata kuliah berpengabdian kepada masyarakat, serta menawarkan berbagai program beasiswa untuk mahasiswanya. Dengan demikian, Itenas dapat membekali mahasiswa dengan kemampuan intelektual, emosional, dan spiritual untuk kesuksesan di masyarakat.", "created_at": "2025-07-22 15:09:07", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 4, "entity": "Misi Itenas", "type": "event", "description": "Misi Itenas adalah tugas yang harus dilakukan oleh Itenas untuk mencapai visi.", "created_at": "2025-07-22 15:09:27", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 5, "entity": "Lab. Material", "type": "organization", "description": "Lab. Material adalah sebuah laboratorium di Itenas.", "created_at": "2025-07-22 15:10:50", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 6, "entity": "Pimpinan Itenas", "type": "person", "description": "Pimpinan Itenas adalah pemimpin yang bertanggung jawab atas semua kegiatan di Itenas.", "created_at": "2025-07-22 15:17:34", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 7, "entity": "UAS", "type": "event", "description": "UAS adalah sebuah kegiatan akademik yang dilakukan oleh mahasiswa di Itenas.", "created_at": "2025-07-22 15:11:09", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 8, "entity": "Logo Itenas", "type": "category", "description": "Logo Itenas adalah simbol yang digunakan oleh Itenas untuk mengidentifikasi diri.", "created_at": "2025-07-22 15:09:28", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 9, "entity": "Wisuda", "type": "event", "description": "Wisuda adalah sebuah acara yang diadakan di Itenas.", "created_at": "2025-07-22 15:14:54", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 10, "entity": "Warga Itenas", "type": "person", "description": "Warga Itenas adalah seluruh unsur yang terdiri dari pimpinan, dosen, tenaga kependidikan dan non kependidikan dan mahasiswa.", "created_at": "2025-07-22 15:17:26", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 11, "entity": "Situs Itenas", "type": "organization", "description": "Situs Itenas adalah sebuah fasilitas yang disediakan oleh Itenas untuk mahasiswa.", "created_at": "2025-07-22 15:11:24", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 12, "entity": "Teknologi Informasi &amp; Komunikasi", "type": "organization", "description": "Teknologi Informasi &amp; Komunikasi adalah salah satu fasilitas di Itenas.", "created_at": "2025-07-22 15:10:14", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 13, "entity": "Lab. Lingkungan", "type": "organization", "description": "Lab. Lingkungan adalah sebuah laboratorium di Itenas.", "created_at": "2025-07-22 15:10:47", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 14, "entity": "Panduan", "type": "category", "description": "Panduan adalah dokumen yang berisi informasi tentang prosedur dan kebijakan di Itenas.", "created_at": "2025-07-22 15:11:20", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 15, "entity": "Repository Itenas", "type": "category", "description": "Repository Itenas adalah sebuah sistem penyimpanan digital yang digunakan untuk menyimpan hasil penelitian mahasiswa.&lt;SEP&gt;Repository Itenas adalah tempat penyimpanan hasil kegiatan pengabdian kepada masyarakat yang dilakukan oleh mahasiswa.", "created_at": "2025-07-22 15:16:56", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 16, "entity": "Desain Interior Itenas", "type": "organization", "description": "Desain Interior Itenas adalah program studi di Itenas.", "created_at": "2025-07-22 15:13:48", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 17, "entity": "Dies Natalis Itenas", "type": "event", "description": "Dies Natalis Itenas adalah sebuah acara yang diadakan di Itenas.&lt;SEP&gt;Dies Natalis Itenas adalah sebuah acara yang diselenggarakan oleh organisasi mahasiswa di Itenas untuk memperingati hari jadi Itenas.", "created_at": "2025-07-22 15:14:54", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 18, "entity": "UTS", "type": "event", "description": "UTS adalah sebuah kegiatan akademik yang dilakukan oleh mahasiswa di Itenas.", "created_at": "2025-07-22 15:11:09", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 19, "entity": "Kampus Itenas", "type": "geo", "description": "Kampus Itenas adalah lokasi fisik di mana kegiatan akademik dan kemahasiswaan berlangsung.", "created_at": "2025-07-22 15:17:27", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 20, "entity": "KM Itenas", "type": "organization", "description": "KM Itenas adalah organisasi kemahasiswaan yang mewakili mahasiswa di Itenas.", "created_at": "2025-07-22 15:17:40", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 21, "entity": "Cabaret Itenas", "type": "organization", "description": "Cabaret Itenas adalah sebuah UKM di Itenas yang berfokus pada pengembangan seni dan teater.&lt;SEP&gt;Cabaret Itenas adalah sebuah unit kegiatan mahasiswa di Itenas yang bergerak di bidang teater.", "created_at": "2025-07-22 15:13:57", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 22, "entity": "Perpustakaan Itenas", "type": "organization", "description": "Perpustakaan Itenas adalah fasilitas yang disediakan oleh Itenas untuk menyimpan dan menyediakan buku dan sumber belajar lainnya.", "created_at": "2025-07-22 15:09:17", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 23, "entity": "Liga Jurusan", "type": "event", "description": "Liga Jurusan adalah sebuah kegiatan olahraga yang diadakan di Itenas.", "created_at": "2025-07-22 15:14:31", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}]
+```
+-----Relationships(KG)-----
+```json
+[{"id": 1, "entity1": "Itenas", "entity2": "Mahasiswa", "description": "Itenas adalah institusi pendidikan tinggi yang menyediakan pendidikan bagi mahasiswa. Mahasiswa adalah bagian dari komunitas Itenas dan harus mematuhi peraturan akademik yang berlaku. Itenas memiliki mahasiswa yang sedang menempuh pendidikan dan menyediakan fasilitas pendukung, termasuk sistem teknologi informasi dan infrastruktur, untuk mendukung kegiatan belajar dan pengembangan diri mahasiswa. Institusi ini juga menyediakan layanan kemahasiswaan dan memiliki berbagai kegiatan akademik untuk mendukung perkembangan mahasiswa. Itenas memiliki peraturan dan kebijakan untuk mahasiswanya, dan mahasiswa harus mematuhi peraturan tersebut untuk melanjutkan studinya. Selain itu, Itenas juga menyelenggarakan pendidikan untuk mahasiswa dan memiliki hak untuk memilih pemenuhan masa dan beban studi. Itenas memberikan penghargaan kepada mahasiswa berprestasi dan memiliki prosedur dan ketentuan yang berlaku untuk mahasiswa, termasuk prosedur cuti kuliah dan ujian khusus. Dengan demikian, Itenas dan mahasiswa memiliki hubungan yang erat dan saling mendukung dalam proses pendidikan dan pengembangan diri.", "created_at": "2025-07-22 15:18:00", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 2, "entity1": "Imadji", "entity2": "Itenas", "description": "Imadji berada di Itenas.", "created_at": "2025-07-22 15:22:08", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 3, "entity1": "Himpunan Mahasiswa Elektro", "entity2": "Itenas", "description": "Himpunan Mahasiswa Elektro berlokasi di Itenas.", "created_at": "2025-07-22 15:20:32", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 4, "entity1": "Himpunan Mahasiswa Teknik Informatika (HMIF)", "entity2": "Itenas", "description": "Himpunan Mahasiswa Teknik Informatika (HMIF) berada di bawah naungan Itenas.", "created_at": "2025-07-22 15:21:17", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 5, "entity1": "HMPL Itenas", "entity2": "Itenas", "description": "HMPL Itenas adalah sebuah organisasi kemahasiswaan yang berlokasi di Itenas.", "created_at": "2025-07-22 15:21:48", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 6, "entity1": "Itenas", "entity2": "Mahasiswa Itenas", "description": "Itenas adalah institusi pendidikan yang memiliki mahasiswa dari berbagai daerah.&lt;SEP&gt;Itenas memiliki mahasiswa yang terdaftar dan memiliki hak dan kewajiban tertentu.&lt;SEP&gt;Itenas memiliki mahasiswa yang terlibat dalam organisasi kemahasiswaan dan memiliki hak dan kewajiban tertentu.", "created_at": "2025-07-22 15:24:36", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 7, "entity1": "Institut Teknologi Nasional", "entity2": "Itenas", "description": "Institut Teknologi Nasional adalah nama lain dari Itenas.", "created_at": "2025-07-22 15:25:41", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 8, "entity1": "HMTI", "entity2": "Itenas", "description": "HMTI adalah sebuah organisasi mahasiswa di ITENAS, sehingga keduanya memiliki hubungan yang erat.", "created_at": "2025-07-22 15:21:01", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 9, "entity1": "Himpunan Mahasiswa", "entity2": "Itenas", "description": "Himpunan Mahasiswa berlokasi di Itenas.", "created_at": "2025-07-22 15:21:33", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 10, "entity1": "HMTK", "entity2": "Itenas", "description": "HMTK adalah sebuah organisasi mahasiswa di ITENAS, sehingga keduanya memiliki hubungan yang erat.", "created_at": "2025-07-22 15:21:11", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 11, "entity1": "HMGD Itenas", "entity2": "Itenas", "description": "HMGD Itenas berlokasi di Itenas.", "created_at": "2025-07-22 15:21:42", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 12, "entity1": "Itenas", "entity2": "Koperasi Mahasiswa (KOPMA)", "description": "Koperasi Mahasiswa (KOPMA) adalah sebuah organisasi mahasiswa di Itenas.", "created_at": "2025-07-22 15:23:21", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 13, "entity1": "Himpunan Mahasiswa Pencinta Alam (HIMPALA)", "entity2": "Itenas", "description": "Himpunan Mahasiswa Pencinta Alam (HIMPALA) adalah sebuah organisasi mahasiswa di Itenas.", "created_at": "2025-07-22 15:23:21", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 14, "entity1": "Fakultas Teknologi Industri (FTI)", "entity2": "Itenas", "description": "Fakultas Teknologi Industri (FTI) adalah salah satu bagian dari Itenas.&lt;SEP&gt;Fakultas Teknologi Industri (FTI) adalah salah satu fakultas di Itenas.&lt;SEP&gt;Itenas memiliki Fakultas Teknologi Industri (FTI) sebagai salah satu fakultasnya.", "created_at": "2025-07-22 15:18:10", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 15, "entity1": "Itenas", "entity2": "Lingkung Seni Sunda (LISENDA)", "description": "Lingkung Seni Sunda (LISENDA) adalah sebuah unit kegiatan mahasiswa di Itenas.", "created_at": "2025-07-22 15:23:06", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 16, "entity1": "Itenas", "entity2": "Keluarga Muslim Itenas (KMI)", "description": "Itenas adalah institut yang memiliki Keluarga Muslim Itenas (KMI) sebagai salah satu organisasi kemahasiswaannya.", "created_at": "2025-07-22 15:22:29", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 17, "entity1": "Itenas", "entity2": "Unit Apresiasi Budaya Minang (UABM)", "description": "Unit Apresiasi Budaya Minang (UABM) adalah sebuah unit kegiatan mahasiswa di Itenas.", "created_at": "2025-07-22 15:23:07", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 18, "entity1": "INKU", "entity2": "Itenas", "description": "INKU adalah sebuah UKM di Itenas.", "created_at": "2025-07-22 15:23:55", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 19, "entity1": "Itenas", "entity2": "Rektor", "description": "Itenas dipimpin oleh Rektor yang bertanggung jawab atas pengelolaan institusi. Rektor di Itenas dipegang oleh Prof. Meilinda Nurbanasari, M.T. Ph.D. yang merupakan pemimpin tertinggi di Itenas dan memiliki kewenangan untuk mengambil keputusan dan memberikan sanksi. Sebagai pemimpin, Rektor bertanggung jawab atas kebijakan dan pengelolaan sistem kredit kemahasiswaan, serta menetapkan kebijakan di Itenas. Rektor juga bertanggung jawab untuk mengatur kebijakan akademik di Itenas, sehingga Rektor memainkan peran penting dalam pengelolaan dan pengembangan institusi Itenas. Dengan demikian, Rektor di Itenas memiliki tanggung jawab yang luas dan kompleks dalam memimpin dan mengelola institusi tersebut.", "created_at": "2025-07-22 15:18:10", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 20, "entity1": "Itenas", "entity2": "Keluarga Mahasiswa Katolik (KMK)", "description": "Itenas adalah institut yang memiliki Keluarga Mahasiswa Katolik (KMK) sebagai salah satu organisasi kemahasiswaannya.", "created_at": "2025-07-22 15:22:29", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 21, "entity1": "Fakultas Teknik Sipil dan Perencanaan (FTSP)", "entity2": "Itenas", "description": "Fakultas Teknik Sipil dan Perencanaan (FTSP) adalah salah satu bagian dari Itenas.&lt;SEP&gt;Itenas memiliki Fakultas Teknik Sipil dan Perencanaan (FTSP) sebagai salah satu fakultasnya.", "created_at": "2025-07-22 15:18:25", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 22, "entity1": "Fakultas Arsitektur dan Desain (FAD)", "entity2": "Itenas", "description": "Fakultas Arsitektur dan Desain (FAD) adalah salah satu bagian dari Itenas.&lt;SEP&gt;Itenas memiliki Fakultas Arsitektur dan Desain (FAD) sebagai salah satu fakultasnya.", "created_at": "2025-07-22 15:18:25", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 23, "entity1": "Dekan", "entity2": "Itenas", "description": "Dekan adalah pejabat yang bertanggung jawab untuk menetapkan predikat kelulusan sangat memuaskan di Itenas.&lt;SEP&gt;Dekan bertanggung jawab untuk menentukan peraturan dan keputusan di Itenas.", "created_at": "2025-07-22 15:25:08", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 24, "entity1": "Biro Akademik", "entity2": "Itenas", "description": "Biro Akademik adalah salah satu biro di Itenas.&lt;SEP&gt;Biro Akademik adalah salah satu organ Itenas yang berfungsi untuk mendukung penyelenggaraan tridarma perguruan tinggi.&lt;SEP&gt;Biro Akademik adalah unit yang bertanggung jawab untuk mengelola administrasi akademik di Itenas.", "created_at": "2025-07-22 15:18:21", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 25, "entity1": "Dosen", "entity2": "Itenas", "description": "Dosen adalah pegawai Itenas yang berfungsi sebagai pendidik profesional dan ilmuwan.", "created_at": "2025-07-22 15:17:59", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 26, "entity1": "Cabaret Itenas", "entity2": "Itenas", "description": "Cabaret Itenas adalah sebuah UKM di Itenas.", "created_at": "2025-07-22 15:23:56", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 27, "entity1": "Itenas", "entity2": "Unit Bola Basket Itenas (UBBI)", "description": "Unit Bola Basket Itenas (UBBI) adalah sebuah organisasi yang bergerak dalam bidang olahraga bola basket di Itenas.", "created_at": "2025-07-22 15:22:42", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 28, "entity1": "Itenas", "entity2": "Taekwondo Itenas", "description": "Taekwondo Itenas adalah sebuah organisasi yang bergerak dalam bidang olahraga taekwondo di Itenas.", "created_at": "2025-07-22 15:22:43", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 29, "entity1": "Bandung", "entity2": "Itenas", "description": "Itenas adalah sebuah institusi pendidikan yang terletak di Bandung, sebuah kota di Jawa Barat. Itenas berlokasi di Bandung dan memiliki alamat Jl. PHH. Mustofa No. 23. Di Itenas, terdapat keputusan tentang peraturan akademik yang ditetapkan di sana. Dengan demikian, Itenas di Bandung merupakan sebuah lembaga pendidikan yang memiliki struktur dan aturan yang jelas, serta berlokasi di sebuah kota yang strategis di Jawa Barat.", "created_at": "2025-07-22 15:17:52", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 30, "entity1": "Itenas", "entity2": "Sanksi", "description": "Itenas memiliki peraturan tentang sanksi yang diberikan kepada mahasiswa yang melanggar peraturan akademik.", "created_at": "2025-07-22 15:25:44", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 31, "entity1": "Fakultas", "entity2": "Itenas", "description": "Fakultas adalah himpunan sumber daya pendukung yang menyelenggarakan dan mengelola program pendidikan akademik di Itenas.&lt;SEP&gt;Itenas memiliki Fakultas sebagai bagian dari struktur organisasinya.&lt;SEP&gt;Itenas terdiri dari beberapa Fakultas yang bertanggung jawab atas pendidikan dan pengajaran mahasiswa.", "created_at": "2025-07-22 15:18:04", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 32, "entity1": "Itenas", "entity2": "Sistem Kredit Kemahasiswaan (SKK)", "description": "Itenas memiliki sistem kredit kemahasiswaan (SKK) untuk mengukur partisipasi mahasiswa dalam kegiatan kemahasiswaan.&lt;SEP&gt;Itenas memiliki sistem kredit kemahasiswaan untuk mengelola kegiatan kokurikuler dan ekstrakurikuler.", "created_at": "2025-07-22 15:25:44", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 33, "entity1": "Itenas", "entity2": "Wakil Rektor Bidang Akademik dan Kemahasiswaan", "description": "Wakil Rektor Bidang Akademik dan Kemahasiswaan bertanggung jawab atas kegiatan akademik dan kemahasiswaan di Itenas.", "created_at": "2025-07-22 15:26:02", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 34, "entity1": "Itenas", "entity2": "Ujian Khusus", "description": "Itenas memiliki prosedur dan ketentuan untuk ujian khusus.", "created_at": "2025-07-22 15:19:50", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 35, "entity1": "Itenas", "entity2": "Program Studi Teknik Mesin", "description": "Program Studi Teknik Mesin adalah sebuah program studi di Itenas.", "created_at": "2025-07-22 15:20:17", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 36, "entity1": "Itenas", "entity2": "Program Studi Teknik Industri", "description": "Program Studi Teknik Industri adalah sebuah program studi di Itenas.", "created_at": "2025-07-22 15:20:18", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 37, "entity1": "Itenas", "entity2": "Program Studi Teknik Sipil", "description": "Program Studi Teknik Sipil adalah sebuah program studi di Itenas.", "created_at": "2025-07-22 15:20:19", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 38, "entity1": "Itenas", "entity2": "Ketua Program Studi", "description": "Ketua Program Studi mengusulkan peraturan dan keputusan di Itenas.", "created_at": "2025-07-22 15:25:08", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 39, "entity1": "Itenas", "entity2": "Kegiatan Kemahasiswaan", "description": "Kegiatan Kemahasiswaan diselenggarakan untuk meningkatkan kualitas dan kemampuan mahasiswa.", "created_at": "2025-07-22 15:25:09", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 40, "entity1": "Himpunan Mahasiswa Prodi", "entity2": "Itenas", "description": "Itenas adalah induk organisasi dari Himpunan Mahasiswa Prodi, yang berada di bawah naungannya.", "created_at": "2025-07-22 15:26:10", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 41, "entity1": "Itenas", "entity2": "Program Studi Desain Interior", "description": "Program Studi Desain Interior adalah salah satu program studi di Itenas.&lt;SEP&gt;Program Studi Desain Interior adalah sebuah program studi di Itenas.", "created_at": "2025-07-22 15:18:42", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 42, "entity1": "Itenas", "entity2": "Kurikulum", "description": "Itenas menyelenggarakan Kurikulum untuk membekali mahasiswa dengan kemampuan akademik.", "created_at": "2025-07-22 15:17:54", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 43, "entity1": "Itenas", "entity2": "Peraturan Akademik", "description": "Itenas memiliki Peraturan Akademik yang mengatur kegiatan akademik.", "created_at": "2025-07-22 15:17:55", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 44, "entity1": "Itenas", "entity2": "Perwalian", "description": "Itenas memiliki sistem perwalian yang terstruktur untuk membantu mahasiswa menyusun matakuliah.", "created_at": "2025-07-22 15:19:36", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 45, "entity1": "Itenas", "entity2": "Program Studi Teknik Elektro", "description": "Program Studi Teknik Elektro adalah sebuah program studi di Itenas.", "created_at": "2025-07-22 15:20:17", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 46, "entity1": "Itenas", "entity2": "Program Studi Teknik Kimia", "description": "Program Studi Teknik Kimia adalah sebuah program studi di Itenas.", "created_at": "2025-07-22 15:20:18", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 47, "entity1": "Itenas", "entity2": "Program Studi Teknik Geodesi", "description": "Program Studi Teknik Geodesi adalah sebuah program studi di Itenas.", "created_at": "2025-07-22 15:20:19", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 48, "entity1": "Itenas", "entity2": "Program Studi Perencanaan Wilayah Dan Kota", "description": "Program Studi Perencanaan Wilayah Dan Kota adalah sebuah program studi di Itenas.", "created_at": "2025-07-22 15:20:20", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 49, "entity1": "Itenas", "entity2": "Program Studi Teknik Lingkungan", "description": "Program Studi Teknik Lingkungan adalah sebuah program studi di Itenas.", "created_at": "2025-07-22 15:20:20", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 50, "entity1": "Itenas", "entity2": "Kei Shin Kan Karate Itenas", "description": "Kei Shin Kan Karate Itenas adalah sebuah organisasi yang bergerak dalam bidang olahraga karate di Itenas.", "created_at": "2025-07-22 15:22:43", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 51, "entity1": "Itenas", "entity2": "Mata Kuliah Berpengabdian Kepada Masyarakat", "description": "Itenas memiliki program studi yang meliputi mata kuliah berpengabdian kepada masyarakat.", "created_at": "2025-07-22 15:25:27", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 52, "entity1": "Itenas", "entity2": "Keluarga Mahasiswa Itenas", "description": "Itenas adalah induk organisasi dari Keluarga Mahasiswa Itenas, yang berada di bawah naungannya.", "created_at": "2025-07-22 15:26:11", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 53, "entity1": "Itenas", "entity2": "Program Studi Desain Produk", "description": "Program Studi Desain Produk adalah salah satu program studi di Itenas.&lt;SEP&gt;Program Studi Desain Produk adalah sebuah program studi di Itenas.", "created_at": "2025-07-22 15:18:42", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 54, "entity1": "Itenas", "entity2": "Program Studi Desain Komunikasi Visual", "description": "Program Studi Desain Komunikasi Visual adalah salah satu program studi di Itenas.&lt;SEP&gt;Program Studi Desain Komunikasi Visual adalah sebuah program studi di Itenas.", "created_at": "2025-07-22 15:18:42", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 55, "entity1": "Itenas", "entity2": "Komisi Disiplin", "description": "Komisi Disiplin adalah sebuah komisi yang dibentuk oleh Rektor untuk menangani pelanggaran norma dan perilaku kehidupan kampus.&lt;SEP&gt;Komisi disiplin adalah tim adhoc yang dibentuk oleh Itenas untuk memberikan pertimbangan dan/atau usul bagi penjatuhan sanksi kepada pegawai dan/atau mahasiswa yang melakukan pelanggaran peraturan.", "created_at": "2025-07-22 15:18:03", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 56, "entity1": "Itenas", "entity2": "UPT Perpustakaan", "description": "UPT Perpustakaan adalah bagian dari Itenas yang bertanggung jawab untuk mengelola perpustakaan.&lt;SEP&gt;UPT Perpustakaan adalah salah satu unit pelaksana teknis Itenas yang berfungsi untuk menyediakan bahan pustaka.", "created_at": "2025-07-22 15:18:21", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 57, "entity1": "Itenas", "entity2": "SKPI", "description": "Itenas menerbitkan SKPI sebagai dokumen yang menunjukkan kemampuan kerja, penguasaan pengetahuan, dan sikap/moral seorang lulusan.", "created_at": "2025-07-22 15:19:59", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 58, "entity1": "Itenas", "entity2": "Jinggaswara", "description": "Jinggaswara adalah sebuah unit kegiatan mahasiswa di Itenas.", "created_at": "2025-07-22 15:23:06", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 59, "entity1": "Itenas", "entity2": "Sivitas Akademika", "description": "Sivitas akademika adalah kelompok atau warga masyarakat akademik yang terdiri atas dosen dan mahasiswa di Itenas.", "created_at": "2025-07-22 15:18:02", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 60, "entity1": "Itenas", "entity2": "Perpustakaan", "description": "Perpustakaan adalah salah satu fasilitas di Itenas.", "created_at": "2025-07-22 15:18:43", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 61, "entity1": "Bank BNI", "entity2": "Itenas", "description": "Itenas bekerja sama dengan Bank BNI untuk menerbitkan Kartu Tanda Mahasiswa (KTM).", "created_at": "2025-07-22 15:19:26", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 62, "entity1": "Biro Akademik (BA)", "entity2": "Itenas", "description": "Itenas memiliki Biro Akademik (BA) yang bertanggung jawab untuk mengurus Kartu Studi Mahasiswa (KSM).", "created_at": "2025-07-22 15:19:40", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 63, "entity1": "Institut", "entity2": "Itenas", "description": "Institut dan Itenas memiliki hubungan sebagai sebuah institut yang menyediakan layanan untuk mahasiswanya.", "created_at": "2025-07-22 15:20:08", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 64, "entity1": "ISEF", "entity2": "Itenas", "description": "ISEF adalah sebuah UKM di Itenas.", "created_at": "2025-07-22 15:23:55", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 65, "entity1": "Itenas", "entity2": "Sistem Kredit Kemahasiswaan", "description": "Sistem Kredit Kemahasiswaan digunakan oleh Itenas untuk menyelenggarakan kegiatan kemahasiswaan.", "created_at": "2025-07-22 15:25:09", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 66, "entity1": "Biro Kemahasiswaan dan Alumni", "entity2": "Itenas", "description": "Biro Kemahasiswaan dan Alumni mengelola kegiatan kemahasiswaan dan alumni di Itenas.", "created_at": "2025-07-22 15:26:03", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 67, "entity1": "Itenas", "entity2": "Unit Kegiatan Mahasiswa", "description": "Itenas adalah induk organisasi dari Unit Kegiatan Mahasiswa, yang berada di bawah naungannya.", "created_at": "2025-07-22 15:26:10", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 68, "entity1": "Fakultas Teknologi Industri", "entity2": "Itenas", "description": "Fakultas Teknologi Industri adalah salah satu fakultas di Itenas.", "created_at": "2025-07-22 15:18:24", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 69, "entity1": "Itenas", "entity2": "Senat Akademik", "description": "Itenas memiliki Senat Akademik yang menjalankan fungsi penyusunan, pertimbangan, dan pengawasan kebijakan akademik.&lt;SEP&gt;Senat akademik adalah badan normatif yang menjalankan fungsi penyusunan, pertimbangan, dan pengawasan kebijakan akademik di Itenas.", "created_at": "2025-07-22 15:18:04", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 70, "entity1": "Dr. Jamaludin, S.Sn., M.Sn.", "entity2": "Itenas", "description": "Dr. Jamaludin adalah Ketua Program Studi Desain Interior di Itenas.&lt;SEP&gt;Dr. Jamaludin adalah bagian dari Itenas sebagai Ketua Program Studi Desain Interior.", "created_at": "2025-07-22 15:18:30", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 71, "entity1": "Dr. Eng. Fitri Suciaty, S.Si., M.Si.", "entity2": "Itenas", "description": "Dr. Eng. Fitri Suciaty adalah Kepala Biro Kerjasama, Hubungan Masyarakat dan Pemasaran di Itenas.&lt;SEP&gt;Dr. Eng. Fitri Suciaty, S.Si., M.Si. adalah seorang dosen atau kepala laboratorium di Itenas.", "created_at": "2025-07-22 15:18:37", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 72, "entity1": "Ali, S.T., M.T.", "entity2": "Itenas", "description": "Ali adalah Kepala Laboratorium Konstruksi Mesin di Itenas.&lt;SEP&gt;Ali, S.T., M.T. adalah seorang dosen atau kepala laboratorium di Itenas.", "created_at": "2025-07-22 15:18:41", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 73, "entity1": "Fadillah Ramadhan, S.T., M.T.", "entity2": "Itena</t>
+  </si>
+  <si>
+    <t>---Role---
+You are a helpful assistant responding to user query about Knowledge Graph and Document Chunks provided in JSON format below.
+---Goal---
+Generate a concise response based on Knowledge Base and follow Response Rules, considering both the conversation history and the current query. Summarize all information in the provided Knowledge Base, and incorporating general knowledge relevant to the Knowledge Base. Do not include information not provided by Knowledge Base.
+When handling relationships with timestamps:
+1. Each relationship has a "created_at" timestamp indicating when we acquired this knowledge
+2. When encountering conflicting relationships, consider both the semantic content and the timestamp
+3. Don't automatically prefer the most recently created relationships - use judgment based on the context
+4. For time-specific queries, prioritize temporal information in the content before considering creation timestamps
+---Conversation History---
+---Knowledge Graph and Document Chunks---
+-----Entities(KG)-----
+```json
+[{"id": 1, "entity": "Itenas", "type": "organization", "description": "Itenas adalah sebuah institusi pendidikan tinggi yang dikenal sebagai Institut Teknologi Nasional. Itenas berada di bawah naungan Yayasan Pendidikan Dayang Sumbi dan memiliki peraturan kemahasiswaan serta keputusan rektor yang jelas. Sebagai sebuah perguruan tinggi, Itenas memiliki berbagai fakultas dan program studi yang menawarkan pendidikan dengan standar yang melebihi standar nasional. Itenas juga memiliki berbagai organisasi kemahasiswaan, termasuk Himpunan Mahasiswa Prodi, Unit Kegiatan Mahasiswa, dan Keluarga Mahasiswa Itenas, yang berfungsi sebagai wadah untuk mengembangkan kemampuan dan kreativitas mahasiswa.\n\nItenas memiliki sistem administrasi akademik yang terstruktur, termasuk Sistem Kredit Semester dan Sistem Kredit Kemahasiswaan, yang digunakan untuk mengukur partisipasi mahasiswa dalam kegiatan kemahasiswaan. Itenas juga menyediakan berbagai layanan dan fasilitas untuk mahasiswanya, termasuk bimbingan dan konseling, pengembangan keprofesian, bantuan asuransi kecelakaan, dana kemahasiswaan, dan layanan kesehatan. Selain itu, Itenas juga memiliki berbagai unit kegiatan mahasiswa dan organisasi kemahasiswaan yang aktif, seperti Himpunan Mahasiswa Pencinta Alam dan Koperasi Mahasiswa.\n\nItenas memiliki peraturan akademik dan sistem kredit kemahasiswaan yang jelas, serta prosedur dan ketentuan untuk mahasiswanya, termasuk prosedur cuti kuliah dan ujian khusus. Itenas juga menerbitkan panduan untuk mahasiswa baru dan mahasiswa secara umum, serta pedoman untuk mahasiswanya. Itenas menyelenggarakan pendidikan dengan menerapkan Sistem Kredit Semester dan Sistem Kredit Kemahasiswaan, dan memiliki berbagai kegiatan akademik, termasuk ujian dan penelitian.\n\nDalam hal kegiatan kemahasiswaan, Itenas menjadi lokasi kegiatan organisasi mahasiswa, seperti Himpunan Mahasiswa Teknik Informatika (HMIF) dan Himpunan Mahasiswa Elektro. Itenas juga menyediakan fasilitas pendukung untuk mahasiswa, termasuk laboratorium, perpustakaan, dan prasarana olahraga. Itenas memiliki berbagai program studi dan mata kuliah berpengabdian kepada masyarakat, serta menawarkan berbagai program beasiswa untuk mahasiswanya. Dengan demikian, Itenas dapat membekali mahasiswa dengan kemampuan intelektual, emosional, dan spiritual untuk kesuksesan di masyarakat.", "created_at": "2025-07-22 15:09:07", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 2, "entity": "Mahasiswa", "type": "person", "description": "Mahasiswa adalah individu yang terdaftar di Institut Teknologi Nasional (Itenas) untuk mengikuti pendidikan. Mereka memiliki hak dan kewajiban sebagai anggota komunitas akademik, termasuk mengikuti proses pembelajaran, menggunakan fasilitas yang disediakan oleh institut, dan berpartisipasi dalam kegiatan akademik dan non-akademik. Mahasiswa Itenas juga dapat menerima penghargaan berdasarkan prestasi akademik dan ekstrakurikuler, serta memiliki hak untuk memilih pemenuhan masa dan beban studi. Mereka diwajibkan untuk memahami dan mengikuti prosedur administrasi akademik, prosedur cuti kuliah, dan ujian khusus. Mahasiswa Itenas terlibat dalam kegiatan kemahasiswaan, kokurikuler, dan ekstrakurikuler untuk mengembangkan soft skill dan kemampuan, serta memiliki kewajiban untuk mengumpulkan poin SKK. Mereka juga berhak menerima ijazah, transkrip akademik, dan surat keterangan pendamping ijazah setelah menyelesaikan pendidikan. Dalam proses pendidikan, mahasiswa Itenas terlibat dalam kegiatan akademik seperti ujian dan penelitian, serta mengikuti program akademik dan pendidikan yang disediakan oleh institut. Secara keseluruhan, mahasiswa Itenas adalah individu yang sedang menempuh pendidikan di Institut Teknologi Nasional, dengan berbagai latar belakang dan minat, dan memiliki hak dan kewajiban untuk mengikuti proses pendidikan dan kegiatan lainnya di institut.", "created_at": "2025-07-22 15:09:17", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 3, "entity": "Ujian Khusus", "type": "event", "description": "Ujian Khusus adalah kegiatan akademik yang dilakukan oleh mahasiswa untuk mengikuti ujian khusus.&lt;SEP&gt;Ujian Khusus adalah sebuah acara yang diadakan untuk mahasiswa yang tidak lulus mata kuliah tertentu.&lt;SEP&gt;Ujian khusus adalah sebuah proses yang memungkinkan mahasiswa untuk mengikuti ujian untuk mata kuliah yang tidak lulus.", "created_at": "2025-07-22 15:11:00", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 4, "entity": "Kegiatan Kemahasiswaan", "type": "event", "description": "Kegiatan Kemahasiswaan adalah acara atau aktivitas yang dilakukan oleh mahasiswa di Itenas.&lt;SEP&gt;Kegiatan Kemahasiswaan adalah acara yang diselenggarakan oleh organisasi kemahasiswaan untuk meningkatkan kemampuan dan kesejahteraan mahasiswa.&lt;SEP&gt;Kegiatan Kemahasiswaan adalah sebuah acara atau kegiatan yang diadakan oleh institusi pendidikan untuk meningkatkan partisipasi mahasiswa.&lt;SEP&gt;Kegiatan Kemahasiswaan adalah sebuah kegiatan yang dilakukan mahasiswa di luar kegiatan akademik di Institut Teknologi Nasional.&lt;SEP&gt;Kegiatan Kemahasiswaan adalah sebuah kegiatan yang diselenggarakan untuk meningkatkan kualitas dan kemampuan mahasiswa.", "created_at": "2025-07-22 15:16:40", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 5, "entity": "Kurikulum", "type": "category", "description": "Kurikulum adalah rencana pembelajaran yang digunakan oleh institusi pendidikan untuk mengatur mata kuliah dan kegiatan pembelajaran.&lt;SEP&gt;Kurikulum adalah sebuah acuan yang digunakan oleh Itenas untuk mengatur proses pendidikan.&lt;SEP&gt;Kurikulum adalah sebuah program yang diselenggarakan oleh Itenas untuk membekali mahasiswa dengan kemampuan akademik.&lt;SEP&gt;Kurikulum adalah sebuah rencana pembelajaran yang digunakan di Institut Teknologi Nasional.&lt;SEP&gt;Kurikulum adalah sebuah sistem pendidikan yang digunakan oleh Itenas untuk mengatur kegiatan akademik mahasiswa.", "created_at": "2025-07-22 15:09:09", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 6, "entity": "SKPI", "type": "category", "description": "SKPI adalah dokumen yang berisi informasi tentang kemajuan studi mahasiswa.&lt;SEP&gt;SKPI adalah dokumen yang menunjukkan kemampuan kerja, penguasaan pengetahuan, dan sikap/moral seorang lulusan.&lt;SEP&gt;SKPI adalah sebuah dokumen yang memuat informasi tentang pencapaian akademik atau kualifikasi dari lulusan pendidikan tinggi.", "created_at": "2025-07-22 15:11:01", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 7, "entity": "Rektor Itenas", "type": "person", "description": "Rektor Itenas adalah pemimpin tertinggi di Itenas yang memiliki wewenang untuk mengesahkan anggaran dasar dan rumah tangga organisasi kemahasiswaan.&lt;SEP&gt;Rektor Itenas adalah pimpinan tertinggi di Itenas yang memimpin institusi tersebut dalam mencapai tujuan pendidikannya.", "created_at": "2025-07-22 15:09:05", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 8, "entity": "Tahun Akademik", "type": "event", "description": "Tahun Akademik adalah sebuah periode waktu yang digunakan untuk mengatur proses pendidikan di Itenas.&lt;SEP&gt;Tahun Akademik adalah sebuah periode waktu yang digunakan untuk menyelenggarakan pendidikan di Itenas.", "created_at": "2025-07-22 15:16:43", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 9, "entity": "Tujuan Itenas", "type": "event", "description": "Tujuan Itenas adalah sasaran yang ingin dicapai oleh Itenas dalam menjalankan kegiatan pendidikan.", "created_at": "2025-07-22 15:09:27", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 10, "entity": "Standar Nasional Pendidikan Tinggi", "type": "category", "description": "Standar Nasional Pendidikan Tinggi adalah sejumlah standar yang ditetapkan oleh pemerintah untuk memastikan kualitas pendidikan tinggi di Indonesia.", "created_at": "2025-07-22 15:09:19", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 11, "entity": "Kegiatan Tridarma", "type": "event", "description": "Kegiatan tridarma adalah kegiatan yang dilakukan oleh perguruan tinggi untuk mencapai tujuan pendidikan.", "created_at": "2025-07-22 15:09:26", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 12, "entity": "Pembelajaran", "type": "category", "description": "Pembelajaran adalah sebuah proses yang digunakan untuk menyelenggarakan pendidikan di Itenas.", "created_at": "2025-07-22 15:16:45", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 13, "entity": "Visi Itenas", "type": "event", "description": "Visi Itenas adalah tujuan yang ingin dicapai oleh Itenas dalam menjalankan kegiatan pendidikan.", "created_at": "2025-07-22 15:09:27", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 14, "entity": "Industri", "type": "category", "description": "Industri adalah sektor ekonomi yang bergerak di bidang produksi barang dan jasa.", "created_at": "2025-07-22 15:17:31", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 15, "entity": "Misi Itenas", "type": "event", "description": "Misi Itenas adalah tugas yang harus dilakukan oleh Itenas untuk mencapai visi.", "created_at": "2025-07-22 15:09:27", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 16, "entity": "Pangkalan Data Pendidikan Tinggi", "type": "organization", "description": "Pangkalan Data Pendidikan Tinggi adalah sebuah basis data yang digunakan untuk mencatat dan mengelola data pendidikan tinggi.", "created_at": "2025-07-22 15:09:20", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 17, "entity": "Panduan", "type": "category", "description": "Panduan adalah dokumen yang berisi informasi tentang prosedur dan kebijakan di Itenas.", "created_at": "2025-07-22 15:11:20", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 18, "entity": "Institut Teknologi", "type": "organization", "description": "Institut Teknologi adalah sebuah bagian dari Itenas yang menyediakan program pendidikan untuk mahasiswa.", "created_at": "2025-07-22 15:11:25", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 19, "entity": "Kriteria Kelulusan", "type": "category", "description": "Kriteria Kelulusan adalah standar yang digunakan untuk menentukan kelulusan mahasiswa.", "created_at": "2025-07-22 15:16:57", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 20, "entity": "Perpustakaan Institut", "type": "organization", "description": "Perpustakaan Institut adalah sebuah fasilitas yang disediakan oleh Itenas untuk mahasiswa.", "created_at": "2025-07-22 15:11:20", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 21, "entity": "Nilai Matakuliah", "type": "category", "description": "Nilai Matakuliah adalah sebuah informasi yang disediakan oleh Itenas untuk mahasiswa.", "created_at": "2025-07-22 15:11:22", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 22, "entity": "Institut Teknologi Nasional", "type": "organization", "description": "Institut Teknologi Nasional adalah nama lain dari Itenas.&lt;SEP&gt;Institut Teknologi Nasional adalah sebuah institusi pendidikan tinggi yang memiliki peraturan akademik untuk program sarjana.&lt;SEP&gt;Institut Teknologi Nasional adalah sebuah perguruan tinggi yang memiliki peraturan kemahasiswaan yang jelas.&lt;SEP&gt;Institut Teknologi Nasional adalah sebuah perguruan tinggi yang memiliki program sarjana dan berbagai kegiatan akademik.", "created_at": "2025-07-22 15:09:13", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 23, "entity": "Pendidikan Tinggi", "type": "category", "description": "Pendidikan Tinggi adalah sebuah kategori yang mencakup berbagai program pendidikan di Institut Teknologi Nasional.&lt;SEP&gt;Pendidikan Tinggi adalah sebuah kategori yang terkait dengan institusi pendidikan tinggi seperti Institut Teknologi Nasional.", "created_at": "2025-07-22 15:16:36", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 24, "entity": "Ilmu Pengetahuan", "type": "category", "description": "Ilmu pengetahuan adalah kategori yang mencakup berbagai bidang ilmu yang diajarkan di perguruan tinggi.", "created_at": "2025-07-22 15:09:25", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 25, "entity": "Pendidikan", "type": "category", "description": "Pendidikan adalah kategori yang mencakup kegiatan dan proses belajar mengajar.&lt;SEP&gt;Pendidikan adalah proses belajar dan mengajar yang diselenggarakan oleh Itenas.", "created_at": "2025-07-22 15:09:13", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}]
+```
+-----Relationships(KG)-----
+```json
+[{"id": 1, "entity1": "Itenas", "entity2": "Mahasiswa", "description": "Itenas adalah institusi pendidikan tinggi yang menyediakan pendidikan bagi mahasiswa. Mahasiswa adalah bagian dari komunitas Itenas dan harus mematuhi peraturan akademik yang berlaku. Itenas memiliki mahasiswa yang sedang menempuh pendidikan dan menyediakan fasilitas pendukung, termasuk sistem teknologi informasi dan infrastruktur, untuk mendukung kegiatan belajar dan pengembangan diri mahasiswa. Institusi ini juga menyediakan layanan kemahasiswaan dan memiliki berbagai kegiatan akademik untuk mendukung perkembangan mahasiswa. Itenas memiliki peraturan dan kebijakan untuk mahasiswanya, dan mahasiswa harus mematuhi peraturan tersebut untuk melanjutkan studinya. Selain itu, Itenas juga menyelenggarakan pendidikan untuk mahasiswa dan memiliki hak untuk memilih pemenuhan masa dan beban studi. Itenas memberikan penghargaan kepada mahasiswa berprestasi dan memiliki prosedur dan ketentuan yang berlaku untuk mahasiswa, termasuk prosedur cuti kuliah dan ujian khusus. Dengan demikian, Itenas dan mahasiswa memiliki hubungan yang erat dan saling mendukung dalam proses pendidikan dan pengembangan diri.", "created_at": "2025-07-22 15:18:00", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 2, "entity1": "Itenas", "entity2": "Ujian Khusus", "description": "Itenas memiliki prosedur dan ketentuan untuk ujian khusus.", "created_at": "2025-07-22 15:19:50", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 3, "entity1": "Itenas", "entity2": "Kegiatan Kemahasiswaan", "description": "Kegiatan Kemahasiswaan diselenggarakan untuk meningkatkan kualitas dan kemampuan mahasiswa.", "created_at": "2025-07-22 15:25:09", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 4, "entity1": "Itenas", "entity2": "Kurikulum", "description": "Itenas menyelenggarakan Kurikulum untuk membekali mahasiswa dengan kemampuan akademik.", "created_at": "2025-07-22 15:17:54", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 5, "entity1": "Itenas", "entity2": "SKPI", "description": "Itenas menerbitkan SKPI sebagai dokumen yang menunjukkan kemampuan kerja, penguasaan pengetahuan, dan sikap/moral seorang lulusan.", "created_at": "2025-07-22 15:19:59", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 6, "entity1": "Itenas", "entity2": "Rektor Itenas", "description": "Rektor Itenas adalah pimpinan tertinggi di Itenas yang memimpin institusi tersebut dalam mencapai tujuan pendidikannya.", "created_at": "2025-07-22 15:17:52", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 7, "entity1": "Itenas", "entity2": "Tahun Akademik", "description": "Tahun Akademik digunakan oleh Itenas untuk menyelenggarakan pendidikan.", "created_at": "2025-07-22 15:25:10", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 8, "entity1": "Itenas", "entity2": "Tujuan Itenas", "description": "Itenas memiliki tujuan yang ingin dicapai dalam menjalankan kegiatan pendidikan.", "created_at": "2025-07-22 15:18:08", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 9, "entity1": "Itenas", "entity2": "Standar Nasional Pendidikan Tinggi", "description": "Standar Nasional Pendidikan Tinggi adalah acuan untuk Itenas dalam menyelenggarakan pendidikan tinggi.", "created_at": "2025-07-22 15:18:01", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 10, "entity1": "Itenas", "entity2": "Kegiatan Tridarma", "description": "Itenas menjalankan kegiatan tridarma untuk mencapai tujuan pendidikan.", "created_at": "2025-07-22 15:18:07", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 11, "entity1": "Itenas", "entity2": "Pembelajaran", "description": "Pembelajaran adalah sebuah proses yang digunakan untuk menyelenggarakan pendidikan di Itenas.", "created_at": "2025-07-22 15:25:09", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 12, "entity1": "Itenas", "entity2": "Visi Itenas", "description": "Itenas memiliki visi yang ingin dicapai dalam menjalankan kegiatan pendidikan.", "created_at": "2025-07-22 15:18:08", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 13, "entity1": "Industri", "entity2": "Itenas", "description": "Industri memiliki hubungan dengan Itenas sebagai institusi pendidikan yang menghasilkan lulusan yang siap bekerja di industri.", "created_at": "2025-07-22 15:26:06", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 14, "entity1": "Itenas", "entity2": "Misi Itenas", "description": "Itenas memiliki misi yang harus dilakukan untuk mencapai visi.", "created_at": "2025-07-22 15:18:08", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 15, "entity1": "Itenas", "entity2": "Pangkalan Data Pendidikan Tinggi", "description": "Pangkalan Data Pendidikan Tinggi adalah sebuah basis data yang digunakan oleh Itenas untuk mencatat dan mengelola data pendidikan tinggi.", "created_at": "2025-07-22 15:18:01", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 16, "entity1": "Itenas", "entity2": "Panduan", "description": "Itenas menerbitkan panduan untuk mahasiswanya.", "created_at": "2025-07-22 15:19:58", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 17, "entity1": "Institut Teknologi", "entity2": "Mahasiswa", "description": "Institut Teknologi menyediakan program pendidikan untuk mahasiswa.", "created_at": "2025-07-22 15:20:04", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 18, "entity1": "Kriteria Kelulusan", "entity2": "Mahasiswa", "description": "Kriteria Kelulusan adalah standar yang digunakan untuk menentukan kelulusan mahasiswa.", "created_at": "2025-07-22 15:25:30", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 19, "entity1": "Mahasiswa", "entity2": "Perpustakaan Institut", "description": "Perpustakaan Institut menyediakan fasilitas untuk mahasiswa.", "created_at": "2025-07-22 15:20:01", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 20, "entity1": "Mahasiswa", "entity2": "Nilai Matakuliah", "description": "Nilai Matakuliah disediakan untuk mahasiswa.", "created_at": "2025-07-22 15:20:02", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 21, "entity1": "Institut Teknologi Nasional", "entity2": "Kurikulum", "description": "Kurikulum digunakan di Institut Teknologi Nasional.", "created_at": "2025-07-22 15:25:02", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 22, "entity1": "Institut Teknologi Nasional", "entity2": "Pendidikan Tinggi", "description": "Institut Teknologi Nasional adalah sebuah institusi pendidikan tinggi yang memiliki peraturan akademik untuk program sarjana.&lt;SEP&gt;Institut Teknologi Nasional menyelenggarakan program Pendidikan Tinggi.", "created_at": "2025-07-22 15:24:56", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 23, "entity1": "Ilmu Pengetahuan", "entity2": "Pendidikan", "description": "Pendidikan dan ilmu pengetahuan adalah dua kategori yang terkait dalam konteks perguruan tinggi.", "created_at": "2025-07-22 15:18:07", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}]
+```
+-----Document Chunks(DC)-----
+```json
+[{"id": 1, "content": "Institut.\n\n--- Halaman 75 ---\n74\n1202\nsanetI\nawsisahaM\nmumU\nnaudnaP\n\n\n5.10.\nAsuransi\nKecelakaan\nSebagai bagian layanan Institut,\nseluruh mahasiswa Itenas diberikan\nasuransi kecelakaan selama 4 tahun\npertama studinya. Layanan ini\nadalah bagian dari kepedulian Insitut\nkepada mahasiswa yang mengalami\nmusibah.\nApabila terjadi kecelakaan,\nmahasiswa atau keluarganya dapat\nmenghubungi Biro Kemahasiswaan\nuntuk mengurus klaim asuransinya\nsesuai dengan peraturan yang\nberlaku.\n\n--- Halaman 76 ---\nB A B VI 75\nORGANISASI\nKEMAHA\nSISWAAN\n“Education is the best friend.\nAn educated person is respected\neverywhere. Education beats\nthe beauty and the youth.”\n- Chanakya\nItenas\nUndergraduate\nGuide\n2021\n\n--- Halaman 77 ---\n76\n1202\nsanetI\nawsisahaM\nmumU\nnaudnaP\n6.2.15\nKeluarga Mahasiswa (K M)\nSTRUKTUR ORGANISASI\nKetua Badan Pengurus : Rafi Piliang\nKepala Departemen Administrasi : Junita Fachriea Gani\nStaff Departemen Administrasi : Dafa Arsyi Damatrana\nKepala Departemen Keuangan : Sofa Jauharotul M.\nStaff Departemen Keuangan : M. Farhan Fadhilah\nKepala Departemen PSDA : Fauzan Miftahuddin\nStaff Departemen PSDA : 1. Ruly Jayakelana\n2. Saeful Hilmi\n3. Shabrina Febrianita\nKepala Departemen Usaha : Niken Indira\nStaff Departemen Usaha : 1. Mirna Nurmala\n2. Kiky Ahmad K.\n3. Indrianti Kurnia\nKepala Departemen Hubungan Masyarakat : Dwi Maulana A.\nStaff Departemen Hubungan Masyarakat : Anto Hermawan\nKepala Dewan Pengawas : Yoga Tri L.\nAnggota Dewan Pengawas : 1. Aditia Adyanugraha A.\n2. Balqish Oktrinanda\n3. Dicky Yusuf Nurjaman\nVISI &amp; MISI Visi : Mewujudkan pergerakan Mahasiswa ITENAS yang\nmenjunjung tinggi unsur solidaritas dan semangat kerakyatan,\ndengan prinsip demokrasi langsung dalam suasana\npersahabatan dan gotong royong.\nMisi :\n1. Mempelopori media yang berkesadaran kemasyarakatan\n2. Menggalang solidaritas dari berbagai komponen mahasiswa\ninternal kampus dengan basis kerakyatan.\n3. Mengembangkan KM ITENAS yang demokratis, partisipatif, dan\nprogresif sebagai wadah bagi seluruh Mahasiswa ITENAS.\nProgram Kerja Kementerian :\nKesekertariatan Kabinet\nKementerian Dalam Negeri\nKementerian Kajian dan Aksi Strategi\nKementerian Keorganisasian dan Pengembangan Sumber Daya\nKementerian Keuangan\nKementerian Luas Negeri\nKementerian Media dan Informasi\n\n--- TABEL ---\n| PROGRAM |\n|---|\n| KERJA |\n\n--- AKHIR TABEL ---\n\n--- Halaman 78 ---\n77\nItenas\nUndergraduate\nGuide\n2021\nUntuk menunjang peningkatan kemampuan\nsoftskill mahasiswa dan membina kemampuan\nberorganisasi serta menggali potensi\nmahasiswa untuk meraih prestasi, Institut\nmendorong adanya kehidupan kemahasiswaan\nyang aktif, dinamis, dan inovatif. Mahasiswa\ndapat menyalurkan aktivitasnya melalui\norganisasi kemahasiswaan yang ada.\n\n\n6.1.\nHimpunan\nMahasiswa Program Studi\nHimpunan Mahasiswa Program Studi (HMP) yang\nberanggotakan seluruh mahasiswa Program Studi, adalah\norganisasi kemahasiswaan di tingkat Program Studi\nyang kegiatan utamanya berdasarkan pada keilmuan dan\nkeprofesian. HMP yang ada saat ini adalah:\n• Himpunan Mahasiswa Program Studi Teknik Elektro (HME)\n• Himpunan Mahasiswa Program Studi Teknik Mesin (HMM)\n• Himpunan Mahasiswa Program Studi Teknik Industri (HMTI)\n• Himpunan Mahasiswa Program Studi Teknik Kimia (HMTK)\n• Himpunan Mahasiswa Program Studi Teknik Informatika (HMIF)\n• Himpunan Mahasiswa Program Studi Teknik Sipil (HMS)\n• Himpunan Mahasiswa Program Studi Teknik Geodesi (HMGD)\n• Himpunan Mahasiswa Program Studi Perencanaan Wilayah Dan Kota (HMPL)\n• Himpunan Mahasiswa Program Studi Teknik Lingkungan (HMTL)\n• Himpunan Mahasiswa Program Studi Desain Interior (IMADJI INTERIOR)\n• Himpunan Mahasiswa Program Studi Desain Produk (PROOF)\n• Himpunan Mahasiswa Program Studi Desain Komunikasi Visual (IMADJI DKV)\n• Himpunan Mahasiswa Program Studi Teknik Arsitektur (HMA)\n\n--- Halaman 79 ---\n78\n1202\nsanetI\nawsisahaM\nmumU\nnaudnaP\nKetua Himpunan Sri Pandu Firdaus 11-2017-073\nSekretaris Himpunan : Riyan Indra Laksono11-2017-007\nBendahara Himpunan : Sandi Ramdani 11-2017-077\nKetua Bidang I : Yusuf Komara Putra", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 2, "content": "angan dan kemandirian.\n\n--- Halaman 16 ---\n15\nItenas\nUndergraduate\nGuide\n2021\nB A B I I\nORGAN\nITENAS\n“Leaders aren’t born, they are made.\nAnd they are made just like anything\nelse, through hard work. And that’s the\nprice we’ll have to pay to achieve that\ngoal, or any goal.”\n- Vince Lombardi\n\n--- Halaman 17 ---\n16\n1202\nsanetI\nawsisahaM\nmumU\nnaudnaP\n\n\n2.1. Susunan Organisasi Itenas\nSenat Akademik\nW\nWak\nSatuan Satuan\nPengembangan Pengawas\nPembelajaran Internal\nLab\nUmum\nProgram Studi Tata Usaha Fakultas\nSatuan\nPenjaminan\nMutu Fakultas\n2.2.Organ Itenas\nOrgan Itenas 1. Rektorat;\nterdiri dari : 2. Senat Akademik Itenas\n3. Fakultas;\n4. Senat Akademik Fakultas\n5. Program Studi\n6. Lembaga Penelitian dan\nPengabdian kepada Masyarakat;\n7. Satuan Penjaminan Mutu;\n8. Satuan Pengembangan\nPembelajaran;\n9.\nSatuan Pengawas Internal;\n10.\nUnit Pelaksana Teknis; dan\n11.\nBiro.\n\n--- TABEL ---\n| Rektorat |  |\n|---|:---|\n| Rektor Wakil Rektor Bidang Akademik dan Kemahasiswaan Wakil Rektor Bidang Keuangan dan Umum kil Rektor Bidang Perencanaan, Inovasi, dan Kerjasama |  |\n|  |  |\n\n--- AKHIR TABEL ---\n\n--- TABEL ---\n|  |  |\n|---|:---|\n\n--- AKHIR TABEL ---\n\n--- TABEL ---\n| Lembaga\nPenelitian dan\nPengabdian\nkepada\nMasyarakat. | Satuan\nPenjaminan\nMutu |\n|---|:---|\n\n--- AKHIR TABEL ---\n\n--- TABEL ---\n| Fakultas |\n|---|\n| Dekan Wakil Dekan Bidang Akademik Wakil Dekan Bidang Kemahasiswaan Wakil Dekan Bidang Sumber Daya |\n\n--- AKHIR TABEL ---\n\n--- TABEL ---\n| Senat Akademik\nFakultas | Unit\nPelaksana\nTeknis | Biro |\n|---|:---|:---|\n\n--- AKHIR TABEL ---\n\n--- TABEL ---\n|  |\n|---|\n| Laboratorium/ Studio Program Studi |\n|  |\n\n--- AKHIR TABEL ---\n\n--- Halaman 18 ---\n17\nItenas\nUndergraduate\nGuide\n2021\n1. Pimpinan\na. Rektor merupakan organ tertinggi dalam susunan organisasi Itenas,\nyang dipimpin oleh Rektor dan dibantu oleh tiga orang Wakil Rektor;\nb. Wakil Rektor Bidang Akademik dan Kemahasiswaan (WRAK)\nSebagai pejabat yang membantu Rektor dalam menjamin\nterlaksananya penyelenggaraan kegiatan tridarma perguruan tinggi\ndan kemahasiswaan dalam rangka mewujudkan visi, misi, dan tujuan\npendidikan Itenas.\nc. Wakil Rektor Bidang Keuangan dan Umum (WRKU)\nSebagai pejabat yang membantu Rektor dalam menjamin\nterlaksananya penyelenggaraan kegiatan keuangan dan umum dalam\nrangka mewujudkan visi, misi, dan tujuan pendidikan Itenas.\nd. Wakil Rektor Bidang Perencanaan, Inovasi, dan Kerja Sama (WRPIK)\nSebagai pejabat yang membantu Rektor dalam menjamin\nterlaksananya perencanaan Itenas secara keseluruhan,\npengembangan inovasi di Itenas, dan penyelenggaraan kerja sama\ndengan berbagai pihak, dalam rangka mewujudkan visi, misi, dan\ntujuan pendidikan Itenas.\ndan Perencanaan (FTSP),\ndan Fakultas Arsitektur\ndan Desain (FAD). Fakultas\ndipimpin oleh Dekan dan\nSenat Akademik Itenas dibantu oleh tiga orang\nadalah badan normatif dan Wakil Dekan serta Kepala\nperwakilan dosen tertinggi Satuan Penjaminan Mutu\ndi bidang akademik yang Fakultas\nberada pada tingkat Institut.\na. Dekan sebagai pemimpin\n3. Fakultas\ntertinggi Fakultas;\nFakultas adalah organ\nb. Wakil Dekan Bidang Akademik\nItenas yang berfungsi untuk\nSebagai pejabat yang\nmengembangkan ilmu\nmembantu Dekan dalam\npengetahuan, teknologi, dan\nmenjamin terlaksananya\nseni dalam rumpun ilmu\npengembangan keilmuan dan\ntertentu serta mengelola\npelaksanaan kegiatan tridarma\nsumber daya. Itenas\nperguruan tinggi.\nmemiliki 3 fakultas, yaitu\nFakultas Teknologi Industri\n(FTI), Fakultas Teknik Sipil\n\n--- TABEL ---\n| 2. Senat Akademik |\n|---|\n| Itenas |\n\n--- AKHIR TABEL ---\n\n--- Halaman 19 ---\n18\n1202\nsanetI\nawsisahaM\nmumU\nnaudnaP\nFAKULTAS dan PROGRAM STUDI di INSTITUT\n\n--- TABEL ---\n| Fakultas | Program Studi |\n|---|:---|\n| Fakultas Teknologi Industri (FTI) | 1. Teknik Elektro |\n|  | 2. Teknik Mesin (S1) 3. Teknik Mesin (S2) |\n|  | 4. Teknik", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": 3, "content": "uhan sanksi kepada pegawai\ndan/atau mahasiswa yang\nmelakukan pelanggaran peraturan.\nAlumni adalah mahasiswa yang\ndinyatakan telah menyelesaikan\npendidikannya pada program\npendidikan yang diselenggarakan\noleh Atenas dan Itenas.\nSenat Akademik adalah badan\nnormatif yang menjalankan fungsi\npenyusunan, pertimbangan, dan\npengawasan kebijakan akademik.\n\n--- Halaman 13 ---\n12\n1202\nsanetI\nawsisahaM\nmumU\nnaudnaP\n\n\n1.2.\nafah\n1.\nItenas menyelenggarakan seluruh\nkegiatan berdasarkan falsafah sebagai\nberikut :\na. Mengajarkan ilmu dan kemampuan kepada\nmasyarakat dan menjadikan masyarakat belajar\nmengenai hal-hal yang diperlukannya dengan\nasas belajar sepanjang hayat;\nb. Membekali kemampuan yang mencakup\naspek intelektual, emosional, dan spiritual, guna\nkesuksesan lulusan di masyarakat;\nc. Memberikan bekal kemampuan pribadi kepada\nlulusan yang bermanfaat bagi peningkatan\nkesejahteraan masyarakat luas.\n2.\nIlmu dan kemampuan yang diperoleh\ndari Itenas, dapat diterapkan oleh para\nlulusannya dengan sebaik-baiknya dan\npenuh tanggung jawab.\n\n--- TABEL ---\n| 1.2. |\n|---|\n|  |\n\n--- AKHIR TABEL ---\n\n--- Halaman 14 ---\n13\nItenas\nUndergraduate\nGuide\n2021\n\n\n1.3.\nVisi, Misi, &amp; Tujuan\nVisi Itenas adalah menjadi perguruan tinggi terkemuka di bidang teknologi,\nsains, dan seni, yang berperan aktif dalam pembangunan berkelanjutan di\nlingkup nasional dan global, berlandaskan nilai-nilai integritas, kualitas, dan\ninovasi yang tinggi.\n1. Membangun karakter bangsa melalui penyelenggaraan kegiatan tridarma\nperguruan tinggi yang berkualitas;\n2. Menghasilkan lulusan yang unggul dalam kecerdasan intelektual serta\nmemiliki integritas dan moral yang tinggi;\n3. Menghasilkan karya ilmiah dan karya inovatif yang bermanfaat bagi\nkesejahteraan masyarakat; dan\n4. Mengembangkan infrastruktur dan sistem manajemen yang berbasis sains\ndan teknologi untuk menumbuhkan suasana akademik yang kondusif.\n1. Mengembangkan potensi sivitas akademika agar menjadi manusia yang\nberiman dan bertakwa kepada Tuhan Yang Maha Esa, berakhlak mulia,\nsehat, berilmu, cakap, kreatif, mandiri, dan menjadi warga negara yang\ndemokratis serta bertanggung jawab;\n2. Membentuk manusia yang berkualitas secara intelektual, spiritual, dan\nemosional, menguasai ilmu pengetahuan, teknologi, dan seni, berlandaskan\npada semangat kebangsaan, sistem nilai, moral, dan watak serta peradaban\nyang mendukung peningkatan daya saing bangsa;\n3. Menyiapkan mahasiswa menjadi warga negara beriman dan berakhlak,\nmemiliki kemampuan akademik dan intelektual dalam bidang ilmu\npengetahuan, teknologi, dan seni, yang memiliki jiwa kewirausahaan dan\nmampu mengembangkan potensi dirinya menjadi insan produktif bagi\nkehidupan pribadi, masyarakat, bangsa, dan umat manusia;\n4. Mengembangkan, menyebarluaskan, dan menerapkan ilmu pengetahuan,\nteknologi, dan seni untuk meningkatkan kesejahteraan masyarakat dan\ndaya saing bangsa, serta memperkaya budaya; dan\n5. Mendorong terjadinya perubahan dan pembaharuan masyarakat yang lebih\nbaik sesuai dengan perkembangan ilmu pengetahuan, teknologi, dan seni.\n\n--- TABEL ---\n|  | ISIV |\n|---|:---|\n\n--- AKHIR TABEL ---\n\n--- TABEL ---\n|  | ISIM |\n|---|:---|\n\n--- AKHIR TABEL ---\n\n--- TABEL ---\n|  | NAUJUT |\n|---|:---|\n\n--- AKHIR TABEL ---\n\n--- Halaman 15 ---\n14\n1202\nsanetI\nawsisahaM\nmumU\nnaudnaP\n\n\n1.4.\nFilosofi &amp; Makna Logo\nBujursangkar berwarna hitam yang\nmerupakan lambang keserbabisaan dan\nmencerminkan potensi</t>
+  </si>
+  <si>
+    <t>---Role---
+You are a helpful assistant responding to user query about Knowledge Graph and Document Chunks provided in JSON format below.
+---Goal---
+Generate a concise response based on Knowledge Base and follow Response Rules, considering both the conversation history and the current query. Summarize all information in the provided Knowledge Base, and incorporating general knowledge relevant to the Knowledge Base. Do not include information not provided by Knowledge Base.
+When handling relationships with timestamps:
+1. Each relationship has a "created_at" timestamp indicating when we acquired this knowledge
+2. When encountering conflicting relationships, consider both the semantic content and the timestamp
+3. Don't automatically prefer the most recently created relationships - use judgment based on the context
+4. For time-specific queries, prioritize temporal information in the content before considering creation timestamps
+---Conversation History---
+---Knowledge Graph and Document Chunks---
+-----Entities(KG)-----
+```json
+[{"id": "1", "entity": "Akademik", "type": "category", "description": "Akademik adalah kegiatan yang terkait dengan pendidikan di Itenas.", "created_at": "2025-07-22 15:09:16", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "2", "entity": "Lab. Multimedia", "type": "organization", "description": "Lab. Multimedia adalah sebuah laboratorium di Itenas.", "created_at": "2025-07-22 15:10:46", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "3", "entity": "Itenas", "type": "organization", "description": "Itenas adalah sebuah institusi pendidikan tinggi yang dikenal sebagai Institut Teknologi Nasional. Itenas berada di bawah naungan Yayasan Pendidikan Dayang Sumbi dan memiliki peraturan kemahasiswaan serta keputusan rektor yang jelas. Sebagai sebuah perguruan tinggi, Itenas memiliki berbagai fakultas dan program studi yang menawarkan pendidikan dengan standar yang melebihi standar nasional. Itenas juga memiliki berbagai organisasi kemahasiswaan, termasuk Himpunan Mahasiswa Prodi, Unit Kegiatan Mahasiswa, dan Keluarga Mahasiswa Itenas, yang berfungsi sebagai wadah untuk mengembangkan kemampuan dan kreativitas mahasiswa.\n\nItenas memiliki sistem administrasi akademik yang terstruktur, termasuk Sistem Kredit Semester dan Sistem Kredit Kemahasiswaan, yang digunakan untuk mengukur partisipasi mahasiswa dalam kegiatan kemahasiswaan. Itenas juga menyediakan berbagai layanan dan fasilitas untuk mahasiswanya, termasuk bimbingan dan konseling, pengembangan keprofesian, bantuan asuransi kecelakaan, dana kemahasiswaan, dan layanan kesehatan. Selain itu, Itenas juga memiliki berbagai unit kegiatan mahasiswa dan organisasi kemahasiswaan yang aktif, seperti Himpunan Mahasiswa Pencinta Alam dan Koperasi Mahasiswa.\n\nItenas memiliki peraturan akademik dan sistem kredit kemahasiswaan yang jelas, serta prosedur dan ketentuan untuk mahasiswanya, termasuk prosedur cuti kuliah dan ujian khusus. Itenas juga menerbitkan panduan untuk mahasiswa baru dan mahasiswa secara umum, serta pedoman untuk mahasiswanya. Itenas menyelenggarakan pendidikan dengan menerapkan Sistem Kredit Semester dan Sistem Kredit Kemahasiswaan, dan memiliki berbagai kegiatan akademik, termasuk ujian dan penelitian.\n\nDalam hal kegiatan kemahasiswaan, Itenas menjadi lokasi kegiatan organisasi mahasiswa, seperti Himpunan Mahasiswa Teknik Informatika (HMIF) dan Himpunan Mahasiswa Elektro. Itenas juga menyediakan fasilitas pendukung untuk mahasiswa, termasuk laboratorium, perpustakaan, dan prasarana olahraga. Itenas memiliki berbagai program studi dan mata kuliah berpengabdian kepada masyarakat, serta menawarkan berbagai program beasiswa untuk mahasiswanya. Dengan demikian, Itenas dapat membekali mahasiswa dengan kemampuan intelektual, emosional, dan spiritual untuk kesuksesan di masyarakat.", "created_at": "2025-07-22 15:09:07", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "4", "entity": "Misi Itenas", "type": "event", "description": "Misi Itenas adalah tugas yang harus dilakukan oleh Itenas untuk mencapai visi.", "created_at": "2025-07-22 15:09:27", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "5", "entity": "Lab. Material", "type": "organization", "description": "Lab. Material adalah sebuah laboratorium di Itenas.", "created_at": "2025-07-22 15:10:50", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "6", "entity": "Pimpinan Itenas", "type": "person", "description": "Pimpinan Itenas adalah pemimpin yang bertanggung jawab atas semua kegiatan di Itenas.", "created_at": "2025-07-22 15:17:34", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "7", "entity": "UAS", "type": "event", "description": "UAS adalah sebuah kegiatan akademik yang dilakukan oleh mahasiswa di Itenas.", "created_at": "2025-07-22 15:11:09", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "8", "entity": "Logo Itenas", "type": "category", "description": "Logo Itenas adalah simbol yang digunakan oleh Itenas untuk mengidentifikasi diri.", "created_at": "2025-07-22 15:09:28", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "9", "entity": "Wisuda", "type": "event", "description": "Wisuda adalah sebuah acara yang diadakan di Itenas.", "created_at": "2025-07-22 15:14:54", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "10", "entity": "Warga Itenas", "type": "person", "description": "Warga Itenas adalah seluruh unsur yang terdiri dari pimpinan, dosen, tenaga kependidikan dan non kependidikan dan mahasiswa.", "created_at": "2025-07-22 15:17:26", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "11", "entity": "Situs Itenas", "type": "organization", "description": "Situs Itenas adalah sebuah fasilitas yang disediakan oleh Itenas untuk mahasiswa.", "created_at": "2025-07-22 15:11:24", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "12", "entity": "Teknologi Informasi &amp; Komunikasi", "type": "organization", "description": "Teknologi Informasi &amp; Komunikasi adalah salah satu fasilitas di Itenas.", "created_at": "2025-07-22 15:10:14", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "13", "entity": "Lab. Lingkungan", "type": "organization", "description": "Lab. Lingkungan adalah sebuah laboratorium di Itenas.", "created_at": "2025-07-22 15:10:47", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "14", "entity": "Panduan", "type": "category", "description": "Panduan adalah dokumen yang berisi informasi tentang prosedur dan kebijakan di Itenas.", "created_at": "2025-07-22 15:11:20", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "15", "entity": "Repository Itenas", "type": "category", "description": "Repository Itenas adalah sebuah sistem penyimpanan digital yang digunakan untuk menyimpan hasil penelitian mahasiswa.&lt;SEP&gt;Repository Itenas adalah tempat penyimpanan hasil kegiatan pengabdian kepada masyarakat yang dilakukan oleh mahasiswa.", "created_at": "2025-07-22 15:16:56", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "16", "entity": "Desain Interior Itenas", "type": "organization", "description": "Desain Interior Itenas adalah program studi di Itenas.", "created_at": "2025-07-22 15:13:48", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "17", "entity": "Dies Natalis Itenas", "type": "event", "description": "Dies Natalis Itenas adalah sebuah acara yang diadakan di Itenas.&lt;SEP&gt;Dies Natalis Itenas adalah sebuah acara yang diselenggarakan oleh organisasi mahasiswa di Itenas untuk memperingati hari jadi Itenas.", "created_at": "2025-07-22 15:14:54", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "18", "entity": "UTS", "type": "event", "description": "UTS adalah sebuah kegiatan akademik yang dilakukan oleh mahasiswa di Itenas.", "created_at": "2025-07-22 15:11:09", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "19", "entity": "Kampus Itenas", "type": "geo", "description": "Kampus Itenas adalah lokasi fisik di mana kegiatan akademik dan kemahasiswaan berlangsung.", "created_at": "2025-07-22 15:17:27", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "20", "entity": "KM Itenas", "type": "organization", "description": "KM Itenas adalah organisasi kemahasiswaan yang mewakili mahasiswa di Itenas.", "created_at": "2025-07-22 15:17:40", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "21", "entity": "Cabaret Itenas", "type": "organization", "description": "Cabaret Itenas adalah sebuah UKM di Itenas yang berfokus pada pengembangan seni dan teater.&lt;SEP&gt;Cabaret Itenas adalah sebuah unit kegiatan mahasiswa di Itenas yang bergerak di bidang teater.", "created_at": "2025-07-22 15:13:57", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "22", "entity": "Perpustakaan Itenas", "type": "organization", "description": "Perpustakaan Itenas adalah fasilitas yang disediakan oleh Itenas untuk menyimpan dan menyediakan buku dan sumber belajar lainnya.", "created_at": "2025-07-22 15:09:17", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "23", "entity": "Liga Jurusan", "type": "event", "description": "Liga Jurusan adalah sebuah kegiatan olahraga yang diadakan di Itenas.", "created_at": "2025-07-22 15:14:31", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "24", "entity": "Mahasiswa", "type": "person", "description": "Mahasiswa adalah individu yang terdaftar di Institut Teknologi Nasional (Itenas) untuk mengikuti pendidikan. Mereka memiliki hak dan kewajiban sebagai anggota komunitas akademik, termasuk mengikuti proses pembelajaran, menggunakan fasilitas yang disediakan oleh institut, dan berpartisipasi dalam kegiatan akademik dan non-akademik. Mahasiswa Itenas juga dapat menerima penghargaan berdasarkan prestasi akademik dan ekstrakurikuler, serta memiliki hak untuk memilih pemenuhan masa dan beban studi. Mereka diwajibkan untuk memahami dan mengikuti prosedur administrasi akademik, prosedur cuti kuliah, dan ujian khusus. Mahasiswa Itenas terlibat dalam kegiatan kemahasiswaan, kokurikuler, dan ekstrakurikuler untuk mengembangkan soft skill dan kemampuan, serta memiliki kewajiban untuk mengumpulkan poin SKK. Mereka juga berhak menerima ijazah, transkrip akademik, dan surat keterangan pendamping ijazah setelah menyelesaikan pendidikan. Dalam proses pendidikan, mahasiswa Itenas terlibat dalam kegiatan akademik seperti ujian dan penelitian, serta mengikuti program akademik dan pendidikan yang disediakan oleh institut. Secara keseluruhan, mahasiswa Itenas adalah individu yang sedang menempuh pendidikan di Institut Teknologi Nasional, dengan berbagai latar belakang dan minat, dan memiliki hak dan kewajiban untuk mengikuti proses pendidikan dan kegiatan lainnya di institut.", "created_at": "2025-07-22 15:09:17", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "25", "entity": "Ujian Khusus", "type": "event", "description": "Ujian Khusus adalah kegiatan akademik yang dilakukan oleh mahasiswa untuk mengikuti ujian khusus.&lt;SEP&gt;Ujian Khusus adalah sebuah acara yang diadakan untuk mahasiswa yang tidak lulus mata kuliah tertentu.&lt;SEP&gt;Ujian khusus adalah sebuah proses yang memungkinkan mahasiswa untuk mengikuti ujian untuk mata kuliah yang tidak lulus.", "created_at": "2025-07-22 15:11:00", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "26", "entity": "Kegiatan Kemahasiswaan", "type": "event", "description": "Kegiatan Kemahasiswaan adalah acara atau aktivitas yang dilakukan oleh mahasiswa di Itenas.&lt;SEP&gt;Kegiatan Kemahasiswaan adalah acara yang diselenggarakan oleh organisasi kemahasiswaan untuk meningkatkan kemampuan dan kesejahteraan mahasiswa.&lt;SEP&gt;Kegiatan Kemahasiswaan adalah sebuah acara atau kegiatan yang diadakan oleh institusi pendidikan untuk meningkatkan partisipasi mahasiswa.&lt;SEP&gt;Kegiatan Kemahasiswaan adalah sebuah kegiatan yang dilakukan mahasiswa di luar kegiatan akademik di Institut Teknologi Nasional.&lt;SEP&gt;Kegiatan Kemahasiswaan adalah sebuah kegiatan yang diselenggarakan untuk meningkatkan kualitas dan kemampuan mahasiswa.", "created_at": "2025-07-22 15:16:40", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "27", "entity": "Kurikulum", "type": "category", "description": "Kurikulum adalah rencana pembelajaran yang digunakan oleh institusi pendidikan untuk mengatur mata kuliah dan kegiatan pembelajaran.&lt;SEP&gt;Kurikulum adalah sebuah acuan yang digunakan oleh Itenas untuk mengatur proses pendidikan.&lt;SEP&gt;Kurikulum adalah sebuah program yang diselenggarakan oleh Itenas untuk membekali mahasiswa dengan kemampuan akademik.&lt;SEP&gt;Kurikulum adalah sebuah rencana pembelajaran yang digunakan di Institut Teknologi Nasional.&lt;SEP&gt;Kurikulum adalah sebuah sistem pendidikan yang digunakan oleh Itenas untuk mengatur kegiatan akademik mahasiswa.", "created_at": "2025-07-22 15:09:09", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "28", "entity": "SKPI", "type": "category", "description": "SKPI adalah dokumen yang berisi informasi tentang kemajuan studi mahasiswa.&lt;SEP&gt;SKPI adalah dokumen yang menunjukkan kemampuan kerja, penguasaan pengetahuan, dan sikap/moral seorang lulusan.&lt;SEP&gt;SKPI adalah sebuah dokumen yang memuat informasi tentang pencapaian akademik atau kualifikasi dari lulusan pendidikan tinggi.", "created_at": "2025-07-22 15:11:01", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "29", "entity": "Rektor Itenas", "type": "person", "description": "Rektor Itenas adalah pemimpin tertinggi di Itenas yang memiliki wewenang untuk mengesahkan anggaran dasar dan rumah tangga organisasi kemahasiswaan.&lt;SEP&gt;Rektor Itenas adalah pimpinan tertinggi di Itenas yang memimpin institusi tersebut dalam mencapai tujuan pendidikannya.", "created_at": "2025-07-22 15:09:05", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "30", "entity": "Tahun Akademik", "type": "event", "description": "Tahun Akademik adalah sebuah periode waktu yang digunakan untuk mengatur proses pendidikan di Itenas.&lt;SEP&gt;Tahun Akademik adalah sebuah periode waktu yang digunakan untuk menyelenggarakan pendidikan di Itenas.", "created_at": "2025-07-22 15:16:43", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "31", "entity": "Tujuan Itenas", "type": "event", "description": "Tujuan Itenas adalah sasaran yang ingin dicapai oleh Itenas dalam menjalankan kegiatan pendidikan.", "created_at": "2025-07-22 15:09:27", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "32", "entity": "Standar Nasional Pendidikan Tinggi", "type": "category", "description": "Standar Nasional Pendidikan Tinggi adalah sejumlah standar yang ditetapkan oleh pemerintah untuk memastikan kualitas pendidikan tinggi di Indonesia.", "created_at": "2025-07-22 15:09:19", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "33", "entity": "Kegiatan Tridarma", "type": "event", "description": "Kegiatan tridarma adalah kegiatan yang dilakukan oleh perguruan tinggi untuk mencapai tujuan pendidikan.", "created_at": "2025-07-22 15:09:26", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "34", "entity": "Pembelajaran", "type": "category", "description": "Pembelajaran adalah sebuah proses yang digunakan untuk menyelenggarakan pendidikan di Itenas.", "created_at": "2025-07-22 15:16:45", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "35", "entity": "Visi Itenas", "type": "event", "description": "Visi Itenas adalah tujuan yang ingin dicapai oleh Itenas dalam menjalankan kegiatan pendidikan.", "created_at": "2025-07-22 15:09:27", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "36", "entity": "Industri", "type": "category", "description": "Industri adalah sektor ekonomi yang bergerak di bidang produksi barang dan jasa.", "created_at": "2025-07-22 15:17:31", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "37", "entity": "Pangkalan Data Pendidikan Tinggi", "type": "organization", "description": "Pangkalan Data Pendidikan Tinggi adalah sebuah basis data yang digunakan untuk mencatat dan mengelola data pendidikan tinggi.", "created_at": "2025-07-22 15:09:20", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "38", "entity": "Institut Teknologi", "type": "organization", "description": "Institut Teknologi adalah sebuah bagian dari Itenas yang menyediakan program pendidikan untuk mahasiswa.", "created_at": "2025-07-22 15:11:25", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "39", "entity": "Kriteria Kelulusan", "type": "category", "description": "Kriteria Kelulusan adalah standar yang digunakan untuk menentukan kelulusan mahasiswa.", "created_at": "2025-07-22 15:16:57", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "40", "entity": "Perpustakaan Institut", "type": "organization", "description": "Perpustakaan Institut adalah sebuah fasilitas yang disediakan oleh Itenas untuk mahasiswa.", "created_at": "2025-07-22 15:11:20", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "41", "entity": "Nilai Matakuliah", "type": "category", "description": "Nilai Matakuliah adalah sebuah informasi yang disediakan oleh Itenas untuk mahasiswa.", "created_at": "2025-07-22 15:11:22", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "42", "entity": "Institut Teknologi Nasional", "type": "organization", "description": "Institut Teknologi Nasional adalah nama lain dari Itenas.&lt;SEP&gt;Institut Teknologi Nasional adalah sebuah institusi pendidikan tinggi yang memiliki peraturan akademik untuk program sarjana.&lt;SEP&gt;Institut Teknologi Nasional adalah sebuah perguruan tinggi yang memiliki peraturan kemahasiswaan yang jelas.&lt;SEP&gt;Institut Teknologi Nasional adalah sebuah perguruan tinggi yang memiliki program sarjana dan berbagai kegiatan akademik.", "created_at": "2025-07-22 15:09:13", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "43", "entity": "Pendidikan Tinggi", "type": "category", "description": "Pendidikan Tinggi adalah sebuah kategori yang mencakup berbagai program pendidikan di Institut Teknologi Nasional.&lt;SEP&gt;Pendidikan Tinggi adalah sebuah kategori yang terkait dengan institusi pendidikan tinggi seperti Institut Teknologi Nasional.", "created_at": "2025-07-22 15:16:36", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "44", "entity": "Ilmu Pengetahuan", "type": "category", "description": "Ilmu pengetahuan adalah kategori yang mencakup berbagai bidang ilmu yang diajarkan di perguruan tinggi.", "created_at": "2025-07-22 15:09:25", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "45", "entity": "Pendidikan", "type": "category", "description": "Pendidikan adalah kategori yang mencakup kegiatan dan proses belajar mengajar.&lt;SEP&gt;Pendidikan adalah proses belajar dan mengajar yang diselenggarakan oleh Itenas.", "created_at": "2025-07-22 15:09:13", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}]
+```
+-----Relationships(KG)-----
+```json
+[{"id": "1", "entity1": "Itenas", "entity2": "Mahasiswa", "description": "Itenas adalah institusi pendidikan tinggi yang menyediakan pendidikan bagi mahasiswa. Mahasiswa adalah bagian dari komunitas Itenas dan harus mematuhi peraturan akademik yang berlaku. Itenas memiliki mahasiswa yang sedang menempuh pendidikan dan menyediakan fasilitas pendukung, termasuk sistem teknologi informasi dan infrastruktur, untuk mendukung kegiatan belajar dan pengembangan diri mahasiswa. Institusi ini juga menyediakan layanan kemahasiswaan dan memiliki berbagai kegiatan akademik untuk mendukung perkembangan mahasiswa. Itenas memiliki peraturan dan kebijakan untuk mahasiswanya, dan mahasiswa harus mematuhi peraturan tersebut untuk melanjutkan studinya. Selain itu, Itenas juga menyelenggarakan pendidikan untuk mahasiswa dan memiliki hak untuk memilih pemenuhan masa dan beban studi. Itenas memberikan penghargaan kepada mahasiswa berprestasi dan memiliki prosedur dan ketentuan yang berlaku untuk mahasiswa, termasuk prosedur cuti kuliah dan ujian khusus. Dengan demikian, Itenas dan mahasiswa memiliki hubungan yang erat dan saling mendukung dalam proses pendidikan dan pengembangan diri.", "created_at": "2025-07-22 15:18:00", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "2", "entity1": "Itenas", "entity2": "Ujian Khusus", "description": "Itenas memiliki prosedur dan ketentuan untuk ujian khusus.", "created_at": "2025-07-22 15:19:50", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "3", "entity1": "Itenas", "entity2": "Kegiatan Kemahasiswaan", "description": "Kegiatan Kemahasiswaan diselenggarakan untuk meningkatkan kualitas dan kemampuan mahasiswa.", "created_at": "2025-07-22 15:25:09", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "4", "entity1": "Itenas", "entity2": "Kurikulum", "description": "Itenas menyelenggarakan Kurikulum untuk membekali mahasiswa dengan kemampuan akademik.", "created_at": "2025-07-22 15:17:54", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "5", "entity1": "Itenas", "entity2": "SKPI", "description": "Itenas menerbitkan SKPI sebagai dokumen yang menunjukkan kemampuan kerja, penguasaan pengetahuan, dan sikap/moral seorang lulusan.", "created_at": "2025-07-22 15:19:59", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "6", "entity1": "Itenas", "entity2": "Rektor Itenas", "description": "Rektor Itenas adalah pimpinan tertinggi di Itenas yang memimpin institusi tersebut dalam mencapai tujuan pendidikannya.", "created_at": "2025-07-22 15:17:52", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "7", "entity1": "Itenas", "entity2": "Tahun Akademik", "description": "Tahun Akademik digunakan oleh Itenas untuk menyelenggarakan pendidikan.", "created_at": "2025-07-22 15:25:10", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "8", "entity1": "Itenas", "entity2": "Tujuan Itenas", "description": "Itenas memiliki tujuan yang ingin dicapai dalam menjalankan kegiatan pendidikan.", "created_at": "2025-07-22 15:18:08", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "9", "entity1": "Itenas", "entity2": "Standar Nasional Pendidikan Tinggi", "description": "Standar Nasional Pendidikan Tinggi adalah acuan untuk Itenas dalam menyelenggarakan pendidikan tinggi.", "created_at": "2025-07-22 15:18:01", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "10", "entity1": "Itenas", "entity2": "Kegiatan Tridarma", "description": "Itenas menjalankan kegiatan tridarma untuk mencapai tujuan pendidikan.", "created_at": "2025-07-22 15:18:07", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "11", "entity1": "Itenas", "entity2": "Pembelajaran", "description": "Pembelajaran adalah sebuah proses yang digunakan untuk menyelenggarakan pendidikan di Itenas.", "created_at": "2025-07-22 15:25:09", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "12", "entity1": "Itenas", "entity2": "Visi Itenas", "description": "Itenas memiliki visi yang ingin dicapai dalam menjalankan kegiatan pendidikan.", "created_at": "2025-07-22 15:18:08", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "13", "entity1": "Industri", "entity2": "Itenas", "description": "Industri memiliki hubungan dengan Itenas sebagai institusi pendidikan yang menghasilkan lulusan yang siap bekerja di industri.", "created_at": "2025-07-22 15:26:06", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "14", "entity1": "Itenas", "entity2": "Misi Itenas", "description": "Itenas memiliki misi yang harus dilakukan untuk mencapai visi.", "created_at": "2025-07-22 15:18:08", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "15", "entity1": "Itenas", "entity2": "Pangkalan Data Pendidikan Tinggi", "description": "Pangkalan Data Pendidikan Tinggi adalah sebuah basis data yang digunakan oleh Itenas untuk mencatat dan mengelola data pendidikan tinggi.", "created_at": "2025-07-22 15:18:01", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "16", "entity1": "Itenas", "entity2": "Panduan", "description": "Itenas menerbitkan panduan untuk mahasiswanya.", "created_at": "2025-07-22 15:19:58", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "17", "entity1": "Institut Teknologi", "entity2": "Mahasiswa", "description": "Institut Teknologi menyediakan program pendidikan untuk mahasiswa.", "created_at": "2025-07-22 15:20:04", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "18", "entity1": "Kriteria Kelulusan", "entity2": "Mahasiswa", "description": "Kriteria Kelulusan adalah standar yang digunakan untuk menentukan kelulusan mahasiswa.", "created_at": "2025-07-22 15:25:30", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "19", "entity1": "Mahasiswa", "entity2": "Perpustakaan Institut", "description": "Perpustakaan Institut menyediakan fasilitas untuk mahasiswa.", "created_at": "2025-07-22 15:20:01", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "20", "entity1": "Mahasiswa", "entity2": "Nilai Matakuliah", "description": "Nilai Matakuliah disediakan untuk mahasiswa.", "created_at": "2025-07-22 15:20:02", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "21", "entity1": "Institut Teknologi Nasional", "entity2": "Kurikulum", "description": "Kurikulum digunakan di Institut Teknologi Nasional.", "created_at": "2025-07-22 15:25:02", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "22", "entity1": "Institut Teknologi Nasional", "entity2": "Pendidikan Tinggi", "description": "Institut Teknologi Nasional adalah sebuah institusi pendidikan tinggi yang memiliki peraturan akademik untuk program sarjana.&lt;SEP&gt;Institut Teknologi Nasional menyelenggarakan program Pendidikan Tinggi.", "created_at": "2025-07-22 15:24:56", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "23", "entity1": "Ilmu Pengetahuan", "entity2": "Pendidikan", "description": "Pendidikan dan ilmu pengetahuan adalah dua kategori yang terkait dalam konteks perguruan tinggi.", "created_at": "2025-07-22 15:18:07", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "24", "entity1": "Imadji", "entity2": "Itenas", "description": "Imadji berada di Itenas.", "created_at": "2025-07-22 15:22:08", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "25", "entity1": "Himpunan Mahasiswa Elektro", "entity2": "Itenas", "description": "Himpunan Mahasiswa Elektro berlokasi di Itenas.", "created_at": "2025-07-22 15:20:32", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "26", "entity1": "Himpunan Mahasiswa Teknik Informatika (HMIF)", "entity2": "Itenas", "description": "Himpunan Mahasiswa Teknik Informatika (HMIF) berada di bawah naungan Itenas.", "created_at": "2025-07-22 15:21:17", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "27", "entity1": "HMPL Itenas", "entity2": "Itenas", "description": "HMPL Itenas adalah sebuah organisasi kemahasiswaan yang berlokasi di Itenas.", "created_at": "2025-07-22 15:21:48", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "28", "entity1": "Itenas", "entity2": "Mahasiswa Itenas", "description": "Itenas adalah institusi pendidikan yang memiliki mahasiswa dari berbagai daerah.&lt;SEP&gt;Itenas memiliki mahasiswa yang terdaftar dan memiliki hak dan kewajiban tertentu.&lt;SEP&gt;Itenas memiliki mahasiswa yang terlibat dalam organisasi kemahasiswaan dan memiliki hak dan kewajiban tertentu.", "created_at": "2025-07-22 15:24:36", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "29", "entity1": "Institut Teknologi Nasional", "entity2": "Itenas", "description": "Institut Teknologi Nasional adalah nama lain dari Itenas.", "created_at": "2025-07-22 15:25:41", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "30", "entity1": "HMTI", "entity2": "Itenas", "description": "HMTI adalah sebuah organisasi mahasiswa di ITENAS, sehingga keduanya memiliki hubungan yang erat.", "created_at": "2025-07-22 15:21:01", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "31", "entity1": "Himpunan Mahasiswa", "entity2": "Itenas", "description": "Himpunan Mahasiswa berlokasi di Itenas.", "created_at": "2025-07-22 15:21:33", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "32", "entity1": "HMTK", "entity2": "Itenas", "description": "HMTK adalah sebuah organisasi mahasiswa di ITENAS, sehingga keduanya memiliki hubungan yang erat.", "created_at": "2025-07-22 15:21:11", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "33", "entity1": "HMGD Itenas", "entity2": "Itenas", "description": "HMGD Itenas berlokasi di Itenas.", "created_at": "2025-07-22 15:21:42", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "34", "entity1": "Itenas", "entity2": "Koperasi Mahasiswa (KOPMA)", "description": "Koperasi Mahasiswa (KOPMA) adalah sebuah organisasi mahasiswa di Itenas.", "created_at": "2025-07-22 15:23:21", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "35", "entity1": "Himpunan Mahasiswa Pencinta Alam (HIMPALA)", "entity2": "Itenas", "description": "Himpunan Mahasiswa Pencinta Alam (HIMPALA) adalah sebuah organisasi mahasiswa di Itenas.", "created_at": "2025-07-22 15:23:21", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "36", "entity1": "Fakultas Teknologi Industri (FTI)", "entity2": "Itenas", "description": "Fakultas Teknologi Industri (FTI) adalah salah satu bagian dari Itenas.&lt;SEP&gt;Fakultas Teknologi Industri (FTI) adalah salah satu fakultas di Itenas.&lt;SEP&gt;Itenas memiliki Fakultas Teknologi Industri (FTI) sebagai salah satu fakultasnya.", "created_at": "2025-07-22 15:18:10", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "37", "entity1": "Itenas", "entity2": "Lingkung Seni Sunda (LISENDA)", "description": "Lingkung Seni Sunda (LISENDA) adalah sebuah unit kegiatan mahasiswa di Itenas.", "created_at": "2025-07-22 15:23:06", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "38", "entity1": "Itenas", "entity2": "Keluarga Muslim Itenas (KMI)", "description": "Itenas adalah institut yang memiliki Keluarga Muslim Itenas (KMI) sebagai salah satu organisasi kemahasiswaannya.", "created_at": "2025-07-22 15:22:29", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "39", "entity1": "Itenas", "entity2": "Unit Apresiasi Budaya Minang (UABM)", "description": "Unit Apresiasi Budaya Minang (UABM) adalah sebuah unit kegiatan mahasiswa di Itenas.", "created_at": "2025-07-22 15:23:07", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "40", "entity1": "INKU", "entity2": "Itenas", "description": "INKU adalah sebuah UKM di Itenas.", "created_at": "2025-07-22 15:23:55", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "41", "entity1": "Itenas", "entity2": "Rektor", "description": "Itenas dipimpin oleh Rektor yang bertanggung jawab atas pengelolaan institusi. Rektor di Itenas dipegang oleh Prof. Meilinda Nurbanasari, M.T. Ph.D. yang merupakan pemimpin tertinggi di Itenas dan memiliki kewenangan untuk mengambil keputusan dan memberikan sanksi. Sebagai pemimpin, Rektor bertanggung jawab atas kebijakan dan pengelolaan sistem kredit kemahasiswaan, serta menetapkan kebijakan di Itenas. Rektor juga bertanggung jawab untuk mengatur kebijakan akademik di Itenas, sehingga Rektor memainkan peran penting dalam pengelolaan dan pengembangan institusi Itenas. Dengan demikian, Rektor di Itenas memiliki tanggung jawab yang luas dan kompleks dalam memimpin dan mengelola institusi tersebut.", "created_at": "2025-07-22 15:18:10", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "42", "entity1": "Itenas", "entity2": "Keluarga Mahasiswa Katolik (KMK)", "description": "Itenas adalah institut yang memiliki Keluarga Mahasiswa Katolik (KMK) sebagai salah satu organisasi kemahasiswaannya.", "created_at": "2025-07-22 15:22:29", "file_path": "pedoman_mahasiswa_clean_revised_collab2.txt"}, {"id": "43", "entity1": "Fakultas Teknik Sipil dan Perencanaan (FTSP)", "entity2": "Itenas", "description": "Fakultas Teknik Sipil dan Perencanaan (FTSP) adalah salah satu bagian dari Itenas.&lt;SEP&gt;Itenas memiliki Fakultas Teknik Sipil dan Perencanaan (FTSP) sebagai salah satu fakultasnya.", "created_at": "2025-07-22 15:18:25", "file_path": "pedoman_mahasiswa_clean_revise</t>
   </si>
 </sst>
 </file>
@@ -426,10 +526,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -457,34 +557,58 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>6799</v>
       </c>
       <c r="G2">
-        <v>21659</v>
+        <v>21628</v>
       </c>
       <c r="H2">
-        <v>13359</v>
+        <v>13350</v>
       </c>
       <c r="I2">
         <v>24119</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
